--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K189"/>
+  <dimension ref="A1:K174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>TIRE_TEMP</t>
+          <t>FRONT_LEFT_WHEEL_RPM</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -550,10 +550,10 @@
         </is>
       </c>
       <c r="E3" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
@@ -570,7 +570,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>BRAKE_TEMP</t>
+          <t>FRONT_RIGHT_WHEEL_RPM</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="E4" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
       <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>ºC</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
@@ -606,17 +606,17 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Message: AQT3</t>
+          <t>Message: AQT7</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x730</t>
+          <t>ID: 0x770</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): Acquisition_Board3</t>
+          <t>Sender(s): Acquisition_Board7</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>TIRE_TEMP</t>
+          <t>SUSP_L</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -715,7 +715,7 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>BRAKE_TEMP</t>
+          <t>SUSP_R</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -751,17 +751,17 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Message: AQT5</t>
+          <t>Message: AQT8</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x750</t>
+          <t>ID: 0x780</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): Acquisition_Board5</t>
+          <t>Sender(s): Acquisition_Board8</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>TIRE_TEMP</t>
+          <t>NTC1</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>0.1</v>
@@ -860,7 +860,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>BRAKE_TEMP</t>
+          <t>NTC2</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>0.1</v>
@@ -892,131 +892,131 @@
       </c>
       <c r="K14" s="3" t="inlineStr"/>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT6</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x760</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board6</t>
-        </is>
-      </c>
-    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>NTC3</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_INV1_Temperatures</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x444</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>TIRE_TEMP</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>BRAKE_TEMP</t>
+          <t>INV1_TempInverter</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E19" s="3" t="b">
@@ -1028,8 +1028,12 @@
       <c r="G19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>ºC</t>
@@ -1037,131 +1041,135 @@
       </c>
       <c r="K19" s="3" t="inlineStr"/>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT7</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x770</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board7</t>
-        </is>
-      </c>
-    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>INV1_TempMotor</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_INV2_Temperatures</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x445</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>SUSP_L</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n"/>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>SUSP_R</t>
+          <t>INV2_TempInverter</t>
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>16</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E24" s="3" t="b">
@@ -1173,8 +1181,12 @@
       <c r="G24" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
+      <c r="H24" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>200</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>ºC</t>
@@ -1182,124 +1194,128 @@
       </c>
       <c r="K24" s="3" t="inlineStr"/>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT8</t>
-        </is>
-      </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x780</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board8</t>
-        </is>
-      </c>
-    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>INV2_TempMotor</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26"/>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Message: PDM_LV</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x210</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): PDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>NTC1</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NTC2</t>
+          <t>LV_Voltage_mV</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>16</v>
@@ -1313,550 +1329,564 @@
         <v>0</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.1</v>
+        <v>0.001</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
+      <c r="J29" s="3" t="n"/>
       <c r="K29" s="3" t="inlineStr"/>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>NTC3</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C30" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Message: PDM_Cooling</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x220</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): PDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>WaterPump_PWM</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E30" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
-    </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_INV1_Temperatures</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x444</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="E33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3" t="n"/>
+      <c r="I33" s="3" t="n"/>
+      <c r="J33" s="3" t="n"/>
+      <c r="K33" s="3" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>INV1_TempInverter</t>
+          <t>CoolingFan_PWM</t>
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E34" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="3" t="n">
-        <v>-55</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr"/>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>INV1_TempMotor</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>-55</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
-    </row>
-    <row r="36"/>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Message: ICD_Result</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x502</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ICD</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_INV2_Temperatures</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x445</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>ICD_Status_OCS</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>INV2_TempInverter</t>
+          <t>ICD_Status_MeasError</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E39" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>INV2_TempMotor</t>
+          <t>ICD_Status_SysError</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E40" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-55</v>
+        <v>0</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr"/>
     </row>
-    <row r="41"/>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>ICD_MsgCounter</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>Message: PDM_LV</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x210</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): PDM</t>
-        </is>
-      </c>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>ICD_Current</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>ICD_Ubat</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>65.535</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Message: ICD_Request</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x500</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): BMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>LV_Voltage_mV</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Req_MuxID</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E44" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="inlineStr"/>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>Message: PDM_Cooling</t>
-        </is>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x220</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): PDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="E47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>WaterPump_PWM</t>
+          <t>Req_OpMode</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>8</v>
@@ -1875,15 +1905,19 @@
       <c r="G48" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
+      <c r="H48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="J48" s="3" t="n"/>
       <c r="K48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CoolingFan_PWM</t>
+          <t>Req_AccessMode</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
@@ -1906,101 +1940,139 @@
       <c r="G49" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
+      <c r="H49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr"/>
     </row>
-    <row r="50"/>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Req_Averaging</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="inlineStr"/>
+    </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>Message: ICD_Result</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x502</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ICD</t>
-        </is>
-      </c>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Req_OCLimitPos</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Req_CanBaudrate</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>ICD_Status_OCS</t>
+          <t>Req_CanIdReq_SN</t>
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E53" s="3" t="b">
@@ -2016,7 +2088,7 @@
         <v>0</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>1</v>
+        <v>16777215</v>
       </c>
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr"/>
@@ -2024,18 +2096,18 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>ICD_Status_MeasError</t>
+          <t>Req_CanIdResp_SN</t>
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E54" s="3" t="b">
@@ -2051,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>1</v>
+        <v>16777215</v>
       </c>
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr"/>
@@ -2059,18 +2131,18 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>ICD_Status_SysError</t>
+          <t>Req_CanIdRes_SN</t>
         </is>
       </c>
       <c r="B55" s="3" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E55" s="3" t="b">
@@ -2086,7 +2158,7 @@
         <v>0</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>1</v>
+        <v>16777215</v>
       </c>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr"/>
@@ -2094,14 +2166,14 @@
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>ICD_MsgCounter</t>
+          <t>Req_NewPw1</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
@@ -2118,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr"/>
@@ -2129,64 +2201,60 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>ICD_Current</t>
+          <t>Req_ResetOption</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E57" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>-2500</v>
+        <v>1</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>ICD_Ubat</t>
+          <t>Req_WakeTimer</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E58" s="3" t="b">
         <v>0</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.001</v>
+        <v>1</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0</v>
@@ -2195,98 +2263,128 @@
         <v>0</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>65.535</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr"/>
     </row>
-    <row r="59"/>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Req_WakeIThreshold</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="inlineStr"/>
+    </row>
     <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>Message: ICD_Request</t>
-        </is>
-      </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x500</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): BMS</t>
-        </is>
-      </c>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Req_WakeAhThreshold</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Req_OpOutputRate</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>65535</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Req_MuxID</t>
+          <t>Req_AccessPw1</t>
         </is>
       </c>
       <c r="B62" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C62" s="3" t="n">
         <v>8</v>
@@ -2317,11 +2415,11 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>Req_OpMode</t>
+          <t>Req_CanMode</t>
         </is>
       </c>
       <c r="B63" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C63" s="3" t="n">
         <v>8</v>
@@ -2344,7 +2442,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J63" s="3" t="n"/>
       <c r="K63" s="3" t="inlineStr"/>
@@ -2352,11 +2450,11 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>Req_AccessMode</t>
+          <t>Req_NewPw2</t>
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C64" s="3" t="n">
         <v>8</v>
@@ -2376,10 +2474,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="J64" s="3" t="n"/>
       <c r="K64" s="3" t="inlineStr"/>
@@ -2387,18 +2485,18 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>Req_Averaging</t>
+          <t>Req_SleepTimer</t>
         </is>
       </c>
       <c r="B65" s="3" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C65" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E65" s="3" t="b">
@@ -2414,26 +2512,30 @@
         <v>0</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J65" s="3" t="n"/>
+        <v>65000</v>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="K65" s="3" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>Req_OCLimitPos</t>
+          <t>Req_AccessPw2</t>
         </is>
       </c>
       <c r="B66" s="3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C66" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E66" s="3" t="b">
@@ -2449,23 +2551,19 @@
         <v>0</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="J66" s="3" t="n"/>
       <c r="K66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Req_CanBaudrate</t>
+          <t>Req_NewPw3</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C67" s="3" t="n">
         <v>8</v>
@@ -2485,10 +2583,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="J67" s="3" t="n"/>
       <c r="K67" s="3" t="inlineStr"/>
@@ -2496,18 +2594,18 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Req_CanIdReq_SN</t>
+          <t>Req_OpInvertCurrent</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E68" s="3" t="b">
@@ -2523,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>16777215</v>
+        <v>1</v>
       </c>
       <c r="J68" s="3" t="n"/>
       <c r="K68" s="3" t="inlineStr"/>
@@ -2531,18 +2629,18 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Req_CanIdResp_SN</t>
+          <t>Req_AccessPw3</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C69" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E69" s="3" t="b">
@@ -2558,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>16777215</v>
+        <v>255</v>
       </c>
       <c r="J69" s="3" t="n"/>
       <c r="K69" s="3" t="inlineStr"/>
@@ -2566,11 +2664,11 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>Req_CanIdRes_SN</t>
+          <t>Req_OCLimitNeg</t>
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C70" s="3" t="n">
         <v>24</v>
@@ -2595,24 +2693,28 @@
       <c r="I70" s="3" t="n">
         <v>16777215</v>
       </c>
-      <c r="J70" s="3" t="n"/>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K70" s="3" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>Req_NewPw1</t>
+          <t>Req_CanIdReq_ID</t>
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E71" s="3" t="b">
@@ -2625,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>126</v>
+        <v>536870911</v>
       </c>
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr"/>
@@ -2636,18 +2738,18 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>Req_ResetOption</t>
+          <t>Req_CanIdResp_ID</t>
         </is>
       </c>
       <c r="B72" s="3" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C72" s="3" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E72" s="3" t="b">
@@ -2660,10 +2762,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>2</v>
+        <v>536870911</v>
       </c>
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr"/>
@@ -2671,18 +2773,18 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>Req_WakeTimer</t>
+          <t>Req_CanIdRes_ID</t>
         </is>
       </c>
       <c r="B73" s="3" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C73" s="3" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E73" s="3" t="b">
@@ -2698,7 +2800,7 @@
         <v>0</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>1</v>
+        <v>536870911</v>
       </c>
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr"/>
@@ -2706,14 +2808,14 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>Req_WakeIThreshold</t>
+          <t>Req_NewPw4</t>
         </is>
       </c>
       <c r="B74" s="3" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="C74" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
@@ -2730,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr"/>
@@ -2741,18 +2843,18 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Req_WakeAhThreshold</t>
+          <t>Req_SleepIThreshold</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E75" s="3" t="b">
@@ -2768,26 +2870,30 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="3" t="n"/>
+        <v>250</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>mA</t>
+        </is>
+      </c>
       <c r="K75" s="3" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>Req_OpOutputRate</t>
+          <t>Req_AccessPw4</t>
         </is>
       </c>
       <c r="B76" s="3" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C76" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E76" s="3" t="b">
@@ -2803,23 +2909,19 @@
         <v>0</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>65535</v>
-      </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="J76" s="3" t="n"/>
       <c r="K76" s="3" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>Req_AccessPw1</t>
+          <t>Req_NewPw5</t>
         </is>
       </c>
       <c r="B77" s="3" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C77" s="3" t="n">
         <v>8</v>
@@ -2839,10 +2941,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr"/>
@@ -2850,11 +2952,11 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>Req_CanMode</t>
+          <t>Req_AccessPw5</t>
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C78" s="3" t="n">
         <v>8</v>
@@ -2877,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr"/>
@@ -2885,11 +2987,11 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>Req_NewPw2</t>
+          <t>Req_NewPw6</t>
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C79" s="3" t="n">
         <v>8</v>
@@ -2920,11 +3022,11 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>Req_SleepTimer</t>
+          <t>Req_SleepAhThreshold</t>
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C80" s="3" t="n">
         <v>16</v>
@@ -2951,7 +3053,7 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>mAs</t>
         </is>
       </c>
       <c r="K80" s="3" t="inlineStr"/>
@@ -2959,11 +3061,11 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>Req_AccessPw2</t>
+          <t>Req_AccessPw6</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C81" s="3" t="n">
         <v>8</v>
@@ -2991,126 +3093,96 @@
       <c r="J81" s="3" t="n"/>
       <c r="K81" s="3" t="inlineStr"/>
     </row>
-    <row r="82">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>Req_NewPw3</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C82" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J82" s="3" t="n"/>
-      <c r="K82" s="3" t="inlineStr"/>
-    </row>
+    <row r="82"/>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>Req_OpInvertCurrent</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="3" t="inlineStr"/>
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>Message: ICD_Response</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x501</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ICD</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>Req_AccessPw3</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C84" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J84" s="3" t="n"/>
-      <c r="K84" s="3" t="inlineStr"/>
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>Req_OCLimitNeg</t>
+          <t>Resp_MuxID</t>
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D85" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E85" s="3" t="b">
@@ -3126,26 +3198,22 @@
         <v>0</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="J85" s="3" t="n"/>
       <c r="K85" s="3" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>Req_CanIdReq_ID</t>
+          <t>Resp_Tchip</t>
         </is>
       </c>
       <c r="B86" s="3" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C86" s="3" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
@@ -3153,31 +3221,35 @@
         </is>
       </c>
       <c r="E86" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G86" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>536870911</v>
-      </c>
-      <c r="J86" s="3" t="n"/>
+        <v>125</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
       <c r="K86" s="3" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>Req_CanIdResp_ID</t>
+          <t>Resp_AhCounter</t>
         </is>
       </c>
       <c r="B87" s="3" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C87" s="3" t="n">
         <v>32</v>
@@ -3188,7 +3260,7 @@
         </is>
       </c>
       <c r="E87" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="3" t="n">
         <v>1</v>
@@ -3197,29 +3269,33 @@
         <v>0</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0</v>
+        <v>-2147483648</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>536870911</v>
-      </c>
-      <c r="J87" s="3" t="n"/>
+        <v>2147483647</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>mAs</t>
+        </is>
+      </c>
       <c r="K87" s="3" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>Req_CanIdRes_ID</t>
+          <t>Resp_OpMode</t>
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E88" s="3" t="b">
@@ -3235,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>536870911</v>
+        <v>2</v>
       </c>
       <c r="J88" s="3" t="n"/>
       <c r="K88" s="3" t="inlineStr"/>
@@ -3243,11 +3319,11 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Req_NewPw4</t>
+          <t>Resp_AccessMode</t>
         </is>
       </c>
       <c r="B89" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C89" s="3" t="n">
         <v>8</v>
@@ -3267,10 +3343,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>126</v>
+        <v>1</v>
       </c>
       <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="inlineStr"/>
@@ -3278,18 +3354,18 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Req_SleepIThreshold</t>
+          <t>Resp_Averaging</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="C90" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E90" s="3" t="b">
@@ -3305,30 +3381,26 @@
         <v>0</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>mA</t>
-        </is>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>Req_AccessPw4</t>
+          <t>Resp_OCLimitPos</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E91" s="3" t="b">
@@ -3344,19 +3416,23 @@
         <v>0</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J91" s="3" t="n"/>
+        <v>16777215</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Req_NewPw5</t>
+          <t>Resp_CanBaudrate</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C92" s="3" t="n">
         <v>8</v>
@@ -3376,10 +3452,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>126</v>
+        <v>2</v>
       </c>
       <c r="J92" s="3" t="n"/>
       <c r="K92" s="3" t="inlineStr"/>
@@ -3387,18 +3463,18 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Req_AccessPw5</t>
+          <t>Resp_CanIdReq_SN</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C93" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D93" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E93" s="3" t="b">
@@ -3414,7 +3490,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>255</v>
+        <v>16777215</v>
       </c>
       <c r="J93" s="3" t="n"/>
       <c r="K93" s="3" t="inlineStr"/>
@@ -3422,18 +3498,18 @@
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Req_NewPw6</t>
+          <t>Resp_CanIdResp_SN</t>
         </is>
       </c>
       <c r="B94" s="3" t="n">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="C94" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E94" s="3" t="b">
@@ -3446,10 +3522,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>126</v>
+        <v>16777215</v>
       </c>
       <c r="J94" s="3" t="n"/>
       <c r="K94" s="3" t="inlineStr"/>
@@ -3457,14 +3533,14 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>Req_SleepAhThreshold</t>
+          <t>Resp_CanIdRes_SN</t>
         </is>
       </c>
       <c r="B95" s="3" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="C95" s="3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
@@ -3484,23 +3560,19 @@
         <v>0</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>65000</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>mAs</t>
-        </is>
-      </c>
+        <v>16777215</v>
+      </c>
+      <c r="J95" s="3" t="n"/>
       <c r="K95" s="3" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>Req_AccessPw6</t>
+          <t>Resp_Pw1</t>
         </is>
       </c>
       <c r="B96" s="3" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="C96" s="3" t="n">
         <v>8</v>
@@ -3520,97 +3592,127 @@
         <v>0</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="J96" s="3" t="n"/>
       <c r="K96" s="3" t="inlineStr"/>
     </row>
-    <row r="97"/>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Resp_ResetOption</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="inlineStr"/>
+    </row>
     <row r="98">
-      <c r="A98" s="1" t="inlineStr">
-        <is>
-          <t>Message: ICD_Response</t>
-        </is>
-      </c>
-      <c r="B98" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x501</t>
-        </is>
-      </c>
-      <c r="C98" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ICD</t>
-        </is>
-      </c>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Resp_WakeTimer</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Resp_DevId_Frame</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Resp_MuxID</t>
+          <t>Resp_FwMajor</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>8</v>
@@ -3627,13 +3729,13 @@
         <v>1</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>255</v>
+        <v>9</v>
       </c>
       <c r="J100" s="3" t="n"/>
       <c r="K100" s="3" t="inlineStr"/>
@@ -3641,14 +3743,14 @@
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>Resp_Tchip</t>
+          <t>Resp_SerialNumber</t>
         </is>
       </c>
       <c r="B101" s="3" t="n">
         <v>15</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
@@ -3656,46 +3758,42 @@
         </is>
       </c>
       <c r="E101" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
+        <v>4294967295</v>
+      </c>
+      <c r="J101" s="3" t="n"/>
       <c r="K101" s="3" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Resp_AhCounter</t>
+          <t>Resp_HwVer_Frame</t>
         </is>
       </c>
       <c r="B102" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C102" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E102" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F102" s="3" t="n">
         <v>1</v>
@@ -3704,33 +3802,29 @@
         <v>0</v>
       </c>
       <c r="H102" s="3" t="n">
-        <v>-2147483648</v>
+        <v>0</v>
       </c>
       <c r="I102" s="3" t="n">
-        <v>2147483647</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>mAs</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J102" s="3" t="n"/>
       <c r="K102" s="3" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>Resp_OpMode</t>
+          <t>Resp_ArticleNumber</t>
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E103" s="3" t="b">
@@ -3746,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>2</v>
+        <v>7.2057594038e+16</v>
       </c>
       <c r="J103" s="3" t="n"/>
       <c r="K103" s="3" t="inlineStr"/>
@@ -3754,18 +3848,18 @@
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>Resp_AccessMode</t>
+          <t>Resp_UpTime</t>
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E104" s="3" t="b">
@@ -3781,26 +3875,30 @@
         <v>0</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J104" s="3" t="n"/>
+        <v>4294967295</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
       <c r="K104" s="3" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>Resp_Averaging</t>
+          <t>Resp_Lifetime</t>
         </is>
       </c>
       <c r="B105" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C105" s="3" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E105" s="3" t="b">
@@ -3816,26 +3914,30 @@
         <v>0</v>
       </c>
       <c r="I105" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J105" s="3" t="n"/>
+        <v>4294967295</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
       <c r="K105" s="3" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Resp_OCLimitPos</t>
+          <t>Resp_EvtMeasType</t>
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E106" s="3" t="b">
@@ -3851,26 +3953,22 @@
         <v>0</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="J106" s="3" t="n"/>
       <c r="K106" s="3" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Resp_CanBaudrate</t>
+          <t>Resp_WakeIThreshold</t>
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
@@ -3890,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J107" s="3" t="n"/>
       <c r="K107" s="3" t="inlineStr"/>
@@ -3898,18 +3996,18 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>Resp_CanIdReq_SN</t>
+          <t>Resp_WakeAhThreshold</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C108" s="3" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E108" s="3" t="b">
@@ -3925,7 +4023,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>16777215</v>
+        <v>1</v>
       </c>
       <c r="J108" s="3" t="n"/>
       <c r="K108" s="3" t="inlineStr"/>
@@ -3933,14 +4031,14 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Resp_CanIdResp_SN</t>
+          <t>Resp_OpOutputRate</t>
         </is>
       </c>
       <c r="B109" s="3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C109" s="3" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
@@ -3960,26 +4058,30 @@
         <v>0</v>
       </c>
       <c r="I109" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J109" s="3" t="n"/>
+        <v>65535</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
       <c r="K109" s="3" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
         <is>
-          <t>Resp_CanIdRes_SN</t>
+          <t>Resp_CanMode</t>
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E110" s="3" t="b">
@@ -3995,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>16777215</v>
+        <v>1</v>
       </c>
       <c r="J110" s="3" t="n"/>
       <c r="K110" s="3" t="inlineStr"/>
@@ -4003,11 +4105,11 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>Resp_Pw1</t>
+          <t>Resp_Pw2</t>
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>8</v>
@@ -4038,18 +4140,18 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>Resp_ResetOption</t>
+          <t>Resp_SleepTimer</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E112" s="3" t="b">
@@ -4062,26 +4164,30 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J112" s="3" t="n"/>
+        <v>65000</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
       <c r="K112" s="3" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>Resp_WakeTimer</t>
+          <t>Resp_DevId_Char1</t>
         </is>
       </c>
       <c r="B113" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C113" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C113" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
@@ -4100,7 +4206,7 @@
         <v>0</v>
       </c>
       <c r="I113" s="3" t="n">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="J113" s="3" t="n"/>
       <c r="K113" s="3" t="inlineStr"/>
@@ -4108,11 +4214,11 @@
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>Resp_DevId_Frame</t>
+          <t>Resp_FwMinor</t>
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>8</v>
@@ -4129,13 +4235,13 @@
         <v>1</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J114" s="3" t="n"/>
       <c r="K114" s="3" t="inlineStr"/>
@@ -4143,11 +4249,11 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>Resp_FwMajor</t>
+          <t>Resp_HwVer_Char1</t>
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>8</v>
@@ -4164,13 +4270,13 @@
         <v>1</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>9</v>
+        <v>255</v>
       </c>
       <c r="J115" s="3" t="n"/>
       <c r="K115" s="3" t="inlineStr"/>
@@ -4178,18 +4284,18 @@
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>Resp_SerialNumber</t>
+          <t>Resp_EvtSysType</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E116" s="3" t="b">
@@ -4205,7 +4311,7 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>4294967295</v>
+        <v>255</v>
       </c>
       <c r="J116" s="3" t="n"/>
       <c r="K116" s="3" t="inlineStr"/>
@@ -4213,53 +4319,57 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>Resp_HwVer_Frame</t>
+          <t>Resp_Text</t>
         </is>
       </c>
       <c r="B117" s="3" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C117" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E117" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G117" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H117" s="3" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="I117" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J117" s="3" t="n"/>
+        <v>125</v>
+      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
       <c r="K117" s="3" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Resp_ArticleNumber</t>
+          <t>Resp_Pw3</t>
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E118" s="3" t="b">
@@ -4272,10 +4382,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>7.2057594038e+16</v>
+        <v>126</v>
       </c>
       <c r="J118" s="3" t="n"/>
       <c r="K118" s="3" t="inlineStr"/>
@@ -4283,18 +4393,18 @@
     <row r="119">
       <c r="A119" s="3" t="inlineStr">
         <is>
-          <t>Resp_UpTime</t>
+          <t>Resp_DevId_Char2</t>
         </is>
       </c>
       <c r="B119" s="3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C119" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E119" s="3" t="b">
@@ -4310,30 +4420,26 @@
         <v>0</v>
       </c>
       <c r="I119" s="3" t="n">
-        <v>4294967295</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="J119" s="3" t="n"/>
       <c r="K119" s="3" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>Resp_Lifetime</t>
+          <t>Resp_FwRelease</t>
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E120" s="3" t="b">
@@ -4343,29 +4449,25 @@
         <v>1</v>
       </c>
       <c r="G120" s="3" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="H120" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="3" t="n">
-        <v>4294967295</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J120" s="3" t="n"/>
       <c r="K120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>Resp_EvtMeasType</t>
+          <t>Resp_HwVer_Char2</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>8</v>
@@ -4396,11 +4498,11 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>Resp_WakeIThreshold</t>
+          <t>Resp_MS_CalibrationData</t>
         </is>
       </c>
       <c r="B122" s="3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>1</v>
@@ -4431,18 +4533,18 @@
     <row r="123">
       <c r="A123" s="3" t="inlineStr">
         <is>
-          <t>Resp_WakeAhThreshold</t>
+          <t>Resp_EvtMeasCount</t>
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D123" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E123" s="3" t="b">
@@ -4458,7 +4560,7 @@
         <v>0</v>
       </c>
       <c r="I123" s="3" t="n">
-        <v>1</v>
+        <v>65535</v>
       </c>
       <c r="J123" s="3" t="n"/>
       <c r="K123" s="3" t="inlineStr"/>
@@ -4466,18 +4568,18 @@
     <row r="124">
       <c r="A124" s="3" t="inlineStr">
         <is>
-          <t>Resp_OpOutputRate</t>
+          <t>Resp_MS_OCSActive</t>
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E124" s="3" t="b">
@@ -4493,26 +4595,22 @@
         <v>0</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>65535</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J124" s="3" t="n"/>
       <c r="K124" s="3" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>Resp_CanMode</t>
+          <t>Resp_OpInvertCurrent</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
@@ -4540,18 +4638,18 @@
     <row r="126">
       <c r="A126" s="3" t="inlineStr">
         <is>
-          <t>Resp_Pw2</t>
+          <t>Resp_OCLimitNeg</t>
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E126" s="3" t="b">
@@ -4564,25 +4662,29 @@
         <v>0</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J126" s="3" t="n"/>
+        <v>16777215</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="K126" s="3" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>Resp_SleepTimer</t>
+          <t>Resp_CanIdReq_ID</t>
         </is>
       </c>
       <c r="B127" s="3" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C127" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D127" s="3" t="inlineStr">
         <is>
@@ -4602,30 +4704,26 @@
         <v>0</v>
       </c>
       <c r="I127" s="3" t="n">
-        <v>65000</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
+        <v>536870911</v>
+      </c>
+      <c r="J127" s="3" t="n"/>
       <c r="K127" s="3" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>Resp_DevId_Char1</t>
+          <t>Resp_CanIdResp_ID</t>
         </is>
       </c>
       <c r="B128" s="3" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C128" s="3" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E128" s="3" t="b">
@@ -4641,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="I128" s="3" t="n">
-        <v>255</v>
+        <v>536870911</v>
       </c>
       <c r="J128" s="3" t="n"/>
       <c r="K128" s="3" t="inlineStr"/>
@@ -4649,18 +4747,18 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>Resp_FwMinor</t>
+          <t>Resp_CanIdRes_ID</t>
         </is>
       </c>
       <c r="B129" s="3" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C129" s="3" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D129" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E129" s="3" t="b">
@@ -4670,13 +4768,13 @@
         <v>1</v>
       </c>
       <c r="G129" s="3" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="H129" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I129" s="3" t="n">
-        <v>9</v>
+        <v>536870911</v>
       </c>
       <c r="J129" s="3" t="n"/>
       <c r="K129" s="3" t="inlineStr"/>
@@ -4684,11 +4782,11 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>Resp_HwVer_Char1</t>
+          <t>Resp_Pw4</t>
         </is>
       </c>
       <c r="B130" s="3" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>8</v>
@@ -4708,10 +4806,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I130" s="3" t="n">
-        <v>255</v>
+        <v>126</v>
       </c>
       <c r="J130" s="3" t="n"/>
       <c r="K130" s="3" t="inlineStr"/>
@@ -4719,18 +4817,18 @@
     <row r="131">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>Resp_EvtSysType</t>
+          <t>Resp_SleepIThreshold</t>
         </is>
       </c>
       <c r="B131" s="3" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="C131" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D131" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E131" s="3" t="b">
@@ -4746,58 +4844,58 @@
         <v>0</v>
       </c>
       <c r="I131" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J131" s="3" t="n"/>
+        <v>250</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>mA</t>
+        </is>
+      </c>
       <c r="K131" s="3" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>Resp_Text</t>
+          <t>Resp_DevId_Char3</t>
         </is>
       </c>
       <c r="B132" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C132" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E132" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G132" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
+        <v>255</v>
+      </c>
+      <c r="J132" s="3" t="n"/>
       <c r="K132" s="3" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>Resp_Pw3</t>
+          <t>Resp_HwVer_Char3</t>
         </is>
       </c>
       <c r="B133" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>8</v>
@@ -4817,10 +4915,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="J133" s="3" t="n"/>
       <c r="K133" s="3" t="inlineStr"/>
@@ -4828,11 +4926,11 @@
     <row r="134">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>Resp_DevId_Char2</t>
+          <t>Resp_Rev_Digit1</t>
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>8</v>
@@ -4849,13 +4947,13 @@
         <v>1</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="H134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>255</v>
+        <v>9</v>
       </c>
       <c r="J134" s="3" t="n"/>
       <c r="K134" s="3" t="inlineStr"/>
@@ -4863,14 +4961,14 @@
     <row r="135">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>Resp_FwRelease</t>
+          <t>Resp_MS_AdcInterrupt</t>
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D135" s="3" t="inlineStr">
         <is>
@@ -4884,13 +4982,13 @@
         <v>1</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="H135" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J135" s="3" t="n"/>
       <c r="K135" s="3" t="inlineStr"/>
@@ -4898,14 +4996,14 @@
     <row r="136">
       <c r="A136" s="3" t="inlineStr">
         <is>
-          <t>Resp_HwVer_Char2</t>
+          <t>Resp_MS_OverflowAdcCh1</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C136" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
@@ -4925,7 +5023,7 @@
         <v>0</v>
       </c>
       <c r="I136" s="3" t="n">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="J136" s="3" t="n"/>
       <c r="K136" s="3" t="inlineStr"/>
@@ -4933,11 +5031,11 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_CalibrationData</t>
+          <t>Resp_MS_OverflowAdcCh2</t>
         </is>
       </c>
       <c r="B137" s="3" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C137" s="3" t="n">
         <v>1</v>
@@ -4968,18 +5066,18 @@
     <row r="138">
       <c r="A138" s="3" t="inlineStr">
         <is>
-          <t>Resp_EvtMeasCount</t>
+          <t>Resp_MS_OverflowAdcCh3</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C138" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E138" s="3" t="b">
@@ -4995,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="I138" s="3" t="n">
-        <v>65535</v>
+        <v>1</v>
       </c>
       <c r="J138" s="3" t="n"/>
       <c r="K138" s="3" t="inlineStr"/>
@@ -5003,11 +5101,11 @@
     <row r="139">
       <c r="A139" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_OCSActive</t>
+          <t>Resp_MS_OpenCircuitI</t>
         </is>
       </c>
       <c r="B139" s="3" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C139" s="3" t="n">
         <v>1</v>
@@ -5038,11 +5136,11 @@
     <row r="140">
       <c r="A140" s="3" t="inlineStr">
         <is>
-          <t>Resp_OpInvertCurrent</t>
+          <t>Resp_MS_OpenCircuitU</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C140" s="3" t="n">
         <v>1</v>
@@ -5073,18 +5171,18 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>Resp_OCLimitNeg</t>
+          <t>Resp_MS_OpenCircuitTchip</t>
         </is>
       </c>
       <c r="B141" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C141" s="3" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E141" s="3" t="b">
@@ -5100,30 +5198,26 @@
         <v>0</v>
       </c>
       <c r="I141" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J141" s="3" t="n"/>
       <c r="K141" s="3" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="3" t="inlineStr">
         <is>
-          <t>Resp_CanIdReq_ID</t>
+          <t>Resp_MS_OpenCircuitText</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
         <v>39</v>
       </c>
       <c r="C142" s="3" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E142" s="3" t="b">
@@ -5139,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="I142" s="3" t="n">
-        <v>536870911</v>
+        <v>1</v>
       </c>
       <c r="J142" s="3" t="n"/>
       <c r="K142" s="3" t="inlineStr"/>
@@ -5147,34 +5241,34 @@
     <row r="143">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>Resp_CanIdResp_ID</t>
+          <t>Resp_Pw5</t>
         </is>
       </c>
       <c r="B143" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C143" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="I143" s="3" t="n">
-        <v>536870911</v>
+        <v>126</v>
       </c>
       <c r="J143" s="3" t="n"/>
       <c r="K143" s="3" t="inlineStr"/>
@@ -5182,18 +5276,18 @@
     <row r="144">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>Resp_CanIdRes_ID</t>
+          <t>Resp_DevId_Char4</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C144" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E144" s="3" t="b">
@@ -5209,7 +5303,7 @@
         <v>0</v>
       </c>
       <c r="I144" s="3" t="n">
-        <v>536870911</v>
+        <v>255</v>
       </c>
       <c r="J144" s="3" t="n"/>
       <c r="K144" s="3" t="inlineStr"/>
@@ -5217,11 +5311,11 @@
     <row r="145">
       <c r="A145" s="3" t="inlineStr">
         <is>
-          <t>Resp_Pw4</t>
+          <t>Resp_HwVer_Char4</t>
         </is>
       </c>
       <c r="B145" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C145" s="3" t="n">
         <v>8</v>
@@ -5241,10 +5335,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I145" s="3" t="n">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="J145" s="3" t="n"/>
       <c r="K145" s="3" t="inlineStr"/>
@@ -5252,18 +5346,18 @@
     <row r="146">
       <c r="A146" s="3" t="inlineStr">
         <is>
-          <t>Resp_SleepIThreshold</t>
+          <t>Resp_Rev_Digit2</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C146" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E146" s="3" t="b">
@@ -5273,32 +5367,28 @@
         <v>1</v>
       </c>
       <c r="G146" s="3" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="H146" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I146" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>mA</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J146" s="3" t="n"/>
       <c r="K146" s="3" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>Resp_DevId_Char3</t>
+          <t>Resp_SS_SystemInit</t>
         </is>
       </c>
       <c r="B147" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C147" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D147" s="3" t="inlineStr">
         <is>
@@ -5318,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="3" t="n">
-        <v>255</v>
+        <v>1</v>
       </c>
       <c r="J147" s="3" t="n"/>
       <c r="K147" s="3" t="inlineStr"/>
@@ -5326,18 +5416,18 @@
     <row r="148">
       <c r="A148" s="3" t="inlineStr">
         <is>
-          <t>Resp_HwVer_Char3</t>
+          <t>Resp_EvtSysCount</t>
         </is>
       </c>
       <c r="B148" s="3" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C148" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E148" s="3" t="b">
@@ -5353,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="I148" s="3" t="n">
-        <v>255</v>
+        <v>65535</v>
       </c>
       <c r="J148" s="3" t="n"/>
       <c r="K148" s="3" t="inlineStr"/>
@@ -5361,14 +5451,14 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t>Resp_Rev_Digit1</t>
+          <t>Resp_SS_Configuration</t>
         </is>
       </c>
       <c r="B149" s="3" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C149" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
@@ -5382,13 +5472,13 @@
         <v>1</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="H149" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I149" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J149" s="3" t="n"/>
       <c r="K149" s="3" t="inlineStr"/>
@@ -5396,11 +5486,11 @@
     <row r="150">
       <c r="A150" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_AdcInterrupt</t>
+          <t>Resp_SS_EepromRW</t>
         </is>
       </c>
       <c r="B150" s="3" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C150" s="3" t="n">
         <v>1</v>
@@ -5431,11 +5521,11 @@
     <row r="151">
       <c r="A151" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_OverflowAdcCh1</t>
+          <t>Resp_SS_PowerOnReset</t>
         </is>
       </c>
       <c r="B151" s="3" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C151" s="3" t="n">
         <v>1</v>
@@ -5466,11 +5556,11 @@
     <row r="152">
       <c r="A152" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_OverflowAdcCh2</t>
+          <t>Resp_SS_LowVoltageReset</t>
         </is>
       </c>
       <c r="B152" s="3" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C152" s="3" t="n">
         <v>1</v>
@@ -5501,11 +5591,11 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_OverflowAdcCh3</t>
+          <t>Resp_SS_ExtPinReset</t>
         </is>
       </c>
       <c r="B153" s="3" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C153" s="3" t="n">
         <v>1</v>
@@ -5536,11 +5626,11 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_OpenCircuitI</t>
+          <t>Resp_SS_ClockMonReset</t>
         </is>
       </c>
       <c r="B154" s="3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C154" s="3" t="n">
         <v>1</v>
@@ -5571,11 +5661,11 @@
     <row r="155">
       <c r="A155" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_OpenCircuitU</t>
+          <t>Resp_SS_CopWdReset</t>
         </is>
       </c>
       <c r="B155" s="3" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C155" s="3" t="n">
         <v>1</v>
@@ -5606,14 +5696,14 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_OpenCircuitTchip</t>
+          <t>Resp_Pw6</t>
         </is>
       </c>
       <c r="B156" s="3" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C156" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
@@ -5630,10 +5720,10 @@
         <v>0</v>
       </c>
       <c r="H156" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I156" s="3" t="n">
-        <v>1</v>
+        <v>126</v>
       </c>
       <c r="J156" s="3" t="n"/>
       <c r="K156" s="3" t="inlineStr"/>
@@ -5641,18 +5731,18 @@
     <row r="157">
       <c r="A157" s="3" t="inlineStr">
         <is>
-          <t>Resp_MS_OpenCircuitText</t>
+          <t>Resp_SleepAhThreshold</t>
         </is>
       </c>
       <c r="B157" s="3" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="C157" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D157" s="3" t="inlineStr">
         <is>
-          <t>Intel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="E157" s="3" t="b">
@@ -5668,19 +5758,23 @@
         <v>0</v>
       </c>
       <c r="I157" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="3" t="n"/>
+        <v>65000</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>mAs</t>
+        </is>
+      </c>
       <c r="K157" s="3" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="3" t="inlineStr">
         <is>
-          <t>Resp_Pw5</t>
+          <t>Resp_DevId_Char5</t>
         </is>
       </c>
       <c r="B158" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C158" s="3" t="n">
         <v>8</v>
@@ -5700,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="I158" s="3" t="n">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="J158" s="3" t="n"/>
       <c r="K158" s="3" t="inlineStr"/>
@@ -5711,11 +5805,11 @@
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
         <is>
-          <t>Resp_DevId_Char4</t>
+          <t>Resp_HwVer_Char5</t>
         </is>
       </c>
       <c r="B159" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C159" s="3" t="n">
         <v>8</v>
@@ -5746,11 +5840,11 @@
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
         <is>
-          <t>Resp_HwVer_Char4</t>
+          <t>Resp_Rev_Digit3</t>
         </is>
       </c>
       <c r="B160" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C160" s="3" t="n">
         <v>8</v>
@@ -5767,13 +5861,13 @@
         <v>1</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="H160" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I160" s="3" t="n">
-        <v>255</v>
+        <v>9</v>
       </c>
       <c r="J160" s="3" t="n"/>
       <c r="K160" s="3" t="inlineStr"/>
@@ -5781,14 +5875,14 @@
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
         <is>
-          <t>Resp_Rev_Digit2</t>
+          <t>Resp_SS_CodeCrc</t>
         </is>
       </c>
       <c r="B161" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C161" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D161" s="3" t="inlineStr">
         <is>
@@ -5802,13 +5896,13 @@
         <v>1</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="H161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I161" s="3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J161" s="3" t="n"/>
       <c r="K161" s="3" t="inlineStr"/>
@@ -5816,11 +5910,11 @@
     <row r="162">
       <c r="A162" s="3" t="inlineStr">
         <is>
-          <t>Resp_SS_SystemInit</t>
+          <t>Resp_SS_CalDataCrc</t>
         </is>
       </c>
       <c r="B162" s="3" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C162" s="3" t="n">
         <v>1</v>
@@ -5851,18 +5945,18 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t>Resp_EvtSysCount</t>
+          <t>Resp_SS_CanRx</t>
         </is>
       </c>
       <c r="B163" s="3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C163" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D163" s="3" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Intel</t>
         </is>
       </c>
       <c r="E163" s="3" t="b">
@@ -5878,7 +5972,7 @@
         <v>0</v>
       </c>
       <c r="I163" s="3" t="n">
-        <v>65535</v>
+        <v>1</v>
       </c>
       <c r="J163" s="3" t="n"/>
       <c r="K163" s="3" t="inlineStr"/>
@@ -5886,11 +5980,11 @@
     <row r="164">
       <c r="A164" s="3" t="inlineStr">
         <is>
-          <t>Resp_SS_Configuration</t>
+          <t>Resp_SS_CanTx</t>
         </is>
       </c>
       <c r="B164" s="3" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="C164" s="3" t="n">
         <v>1</v>
@@ -5921,11 +6015,11 @@
     <row r="165">
       <c r="A165" s="3" t="inlineStr">
         <is>
-          <t>Resp_SS_EepromRW</t>
+          <t>Resp_SS_Overtemp</t>
         </is>
       </c>
       <c r="B165" s="3" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C165" s="3" t="n">
         <v>1</v>
@@ -5956,11 +6050,11 @@
     <row r="166">
       <c r="A166" s="3" t="inlineStr">
         <is>
-          <t>Resp_SS_PowerOnReset</t>
+          <t>Resp_SS_Undertemp</t>
         </is>
       </c>
       <c r="B166" s="3" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="C166" s="3" t="n">
         <v>1</v>
@@ -5991,11 +6085,11 @@
     <row r="167">
       <c r="A167" s="3" t="inlineStr">
         <is>
-          <t>Resp_SS_LowVoltageReset</t>
+          <t>Resp_SS_PowerFailure</t>
         </is>
       </c>
       <c r="B167" s="3" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C167" s="3" t="n">
         <v>1</v>
@@ -6026,11 +6120,11 @@
     <row r="168">
       <c r="A168" s="3" t="inlineStr">
         <is>
-          <t>Resp_SS_ExtPinReset</t>
+          <t>Resp_SS_SystemClock</t>
         </is>
       </c>
       <c r="B168" s="3" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C168" s="3" t="n">
         <v>1</v>
@@ -6061,14 +6155,14 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t>Resp_SS_ClockMonReset</t>
+          <t>Resp_HwVer_Char6</t>
         </is>
       </c>
       <c r="B169" s="3" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C169" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D169" s="3" t="inlineStr">
         <is>
@@ -6088,7 +6182,7 @@
         <v>0</v>
       </c>
       <c r="I169" s="3" t="n">
-        <v>1</v>
+        <v>255</v>
       </c>
       <c r="J169" s="3" t="n"/>
       <c r="K169" s="3" t="inlineStr"/>
@@ -6096,14 +6190,14 @@
     <row r="170">
       <c r="A170" s="3" t="inlineStr">
         <is>
-          <t>Resp_SS_CopWdReset</t>
+          <t>Resp_Rev_Digit4</t>
         </is>
       </c>
       <c r="B170" s="3" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C170" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
@@ -6117,134 +6211,100 @@
         <v>1</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="H170" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I170" s="3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J170" s="3" t="n"/>
       <c r="K170" s="3" t="inlineStr"/>
     </row>
-    <row r="171">
-      <c r="A171" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Pw6</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C171" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F171" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G171" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H171" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I171" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J171" s="3" t="n"/>
-      <c r="K171" s="3" t="inlineStr"/>
-    </row>
+    <row r="171"/>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SleepAhThreshold</t>
-        </is>
-      </c>
-      <c r="B172" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="C172" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F172" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G172" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H172" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I172" s="3" t="n">
-        <v>65000</v>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>mAs</t>
-        </is>
-      </c>
-      <c r="K172" s="3" t="inlineStr"/>
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT1</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x700</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Acquisition_Board1</t>
+        </is>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="inlineStr">
-        <is>
-          <t>Resp_DevId_Char5</t>
-        </is>
-      </c>
-      <c r="B173" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C173" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F173" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G173" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H173" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I173" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J173" s="3" t="n"/>
-      <c r="K173" s="3" t="inlineStr"/>
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="inlineStr">
         <is>
-          <t>Resp_HwVer_Char5</t>
+          <t>Throtle_Percentage</t>
         </is>
       </c>
       <c r="B174" s="3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C174" s="3" t="n">
         <v>8</v>
@@ -6263,505 +6323,10 @@
       <c r="G174" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H174" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I174" s="3" t="n">
-        <v>255</v>
-      </c>
+      <c r="H174" s="3" t="n"/>
+      <c r="I174" s="3" t="n"/>
       <c r="J174" s="3" t="n"/>
       <c r="K174" s="3" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Rev_Digit3</t>
-        </is>
-      </c>
-      <c r="B175" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C175" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F175" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G175" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="H175" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I175" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J175" s="3" t="n"/>
-      <c r="K175" s="3" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_CodeCrc</t>
-        </is>
-      </c>
-      <c r="B176" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C176" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F176" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G176" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H176" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I176" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J176" s="3" t="n"/>
-      <c r="K176" s="3" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_CalDataCrc</t>
-        </is>
-      </c>
-      <c r="B177" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="C177" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F177" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I177" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J177" s="3" t="n"/>
-      <c r="K177" s="3" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_CanRx</t>
-        </is>
-      </c>
-      <c r="B178" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="C178" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F178" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G178" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I178" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J178" s="3" t="n"/>
-      <c r="K178" s="3" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_CanTx</t>
-        </is>
-      </c>
-      <c r="B179" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="C179" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F179" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H179" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I179" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J179" s="3" t="n"/>
-      <c r="K179" s="3" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_Overtemp</t>
-        </is>
-      </c>
-      <c r="B180" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="C180" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F180" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G180" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H180" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I180" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J180" s="3" t="n"/>
-      <c r="K180" s="3" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_Undertemp</t>
-        </is>
-      </c>
-      <c r="B181" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="C181" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F181" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G181" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J181" s="3" t="n"/>
-      <c r="K181" s="3" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_PowerFailure</t>
-        </is>
-      </c>
-      <c r="B182" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="C182" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F182" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G182" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H182" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I182" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J182" s="3" t="n"/>
-      <c r="K182" s="3" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_SystemClock</t>
-        </is>
-      </c>
-      <c r="B183" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="C183" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F183" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H183" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I183" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J183" s="3" t="n"/>
-      <c r="K183" s="3" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="inlineStr">
-        <is>
-          <t>Resp_HwVer_Char6</t>
-        </is>
-      </c>
-      <c r="B184" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C184" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F184" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G184" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H184" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I184" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J184" s="3" t="n"/>
-      <c r="K184" s="3" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Rev_Digit4</t>
-        </is>
-      </c>
-      <c r="B185" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C185" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F185" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G185" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="H185" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I185" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J185" s="3" t="n"/>
-      <c r="K185" s="3" t="inlineStr"/>
-    </row>
-    <row r="186"/>
-    <row r="187">
-      <c r="A187" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT1</t>
-        </is>
-      </c>
-      <c r="B187" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x700</t>
-        </is>
-      </c>
-      <c r="C187" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board1</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K188" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="inlineStr">
-        <is>
-          <t>Throtle_Percentage</t>
-        </is>
-      </c>
-      <c r="B189" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C189" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F189" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H189" s="3" t="n"/>
-      <c r="I189" s="3" t="n"/>
-      <c r="J189" s="3" t="n"/>
-      <c r="K189" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -553,7 +553,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -7,12 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="data_t26" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="FSIC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="handcart_t26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="autonomous_t26" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="powertrain_t26" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="aquisition_boards" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="FSIC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="handcart_t26" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="autonomous_t26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="powertrain_t26" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="aquisition_boards" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,5903 +441,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K174"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT2</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x720</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board2</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>FRONT_LEFT_WHEEL_RPM</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>FRONT_RIGHT_WHEEL_RPM</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT7</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x770</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>SUSP_L</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>SUSP_R</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT8</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x780</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board8</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>NTC1</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>NTC2</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>NTC3</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_INV1_Temperatures</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x444</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>INV1_TempInverter</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3" t="n">
-        <v>-55</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>INV1_TempMotor</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G20" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>-55</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_INV2_Temperatures</t>
-        </is>
-      </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x445</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>INV2_TempInverter</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G24" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>-55</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>INV2_TempMotor</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>-55</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>ºC</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>Message: PDM_LV</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x210</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): PDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>LV_Voltage_mV</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>Message: PDM_Cooling</t>
-        </is>
-      </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x220</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): PDM</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>WaterPump_PWM</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>CoolingFan_PWM</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
-      <c r="J34" s="3" t="n"/>
-      <c r="K34" s="3" t="inlineStr"/>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>Message: ICD_Result</t>
-        </is>
-      </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x502</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ICD</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>ICD_Status_OCS</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="3" t="n"/>
-      <c r="K38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>ICD_Status_MeasError</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="3" t="n"/>
-      <c r="K39" s="3" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>ICD_Status_SysError</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>ICD_MsgCounter</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>ICD_Current</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>-2500</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>ICD_Ubat</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>65.535</v>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>Message: ICD_Request</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x500</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): BMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Req_MuxID</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>Req_OpMode</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C48" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Req_AccessMode</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C49" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Req_Averaging</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C50" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>Req_OCLimitPos</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C51" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K51" s="3" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Req_CanBaudrate</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C52" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J52" s="3" t="n"/>
-      <c r="K52" s="3" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Req_CanIdReq_SN</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Req_CanIdResp_SN</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Req_CanIdRes_SN</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Req_NewPw1</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C56" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J56" s="3" t="n"/>
-      <c r="K56" s="3" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Req_ResetOption</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C57" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J57" s="3" t="n"/>
-      <c r="K57" s="3" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Req_WakeTimer</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="3" t="n"/>
-      <c r="K58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>Req_WakeIThreshold</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="3" t="n"/>
-      <c r="K59" s="3" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>Req_WakeAhThreshold</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="n"/>
-      <c r="K60" s="3" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
-        <is>
-          <t>Req_OpOutputRate</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3" t="n">
-        <v>65535</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
-      <c r="K61" s="3" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>Req_AccessPw1</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C62" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="3" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>Req_CanMode</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Req_NewPw2</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J64" s="3" t="n"/>
-      <c r="K64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Req_SleepTimer</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>65000</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Req_AccessPw2</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J66" s="3" t="n"/>
-      <c r="K66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Req_NewPw3</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C67" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J67" s="3" t="n"/>
-      <c r="K67" s="3" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Req_OpInvertCurrent</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="3" t="n"/>
-      <c r="K68" s="3" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>Req_AccessPw3</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J69" s="3" t="n"/>
-      <c r="K69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Req_OCLimitNeg</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Req_CanIdReq_ID</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>536870911</v>
-      </c>
-      <c r="J71" s="3" t="n"/>
-      <c r="K71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>Req_CanIdResp_ID</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C72" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>536870911</v>
-      </c>
-      <c r="J72" s="3" t="n"/>
-      <c r="K72" s="3" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Req_CanIdRes_ID</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C73" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>536870911</v>
-      </c>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>Req_NewPw4</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C74" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J74" s="3" t="n"/>
-      <c r="K74" s="3" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>Req_SleepIThreshold</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C75" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>mA</t>
-        </is>
-      </c>
-      <c r="K75" s="3" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>Req_AccessPw4</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C76" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J76" s="3" t="n"/>
-      <c r="K76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>Req_NewPw5</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J77" s="3" t="n"/>
-      <c r="K77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>Req_AccessPw5</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C78" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="3" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>Req_NewPw6</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C79" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H79" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>Req_SleepAhThreshold</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="C80" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>65000</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>mAs</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>Req_AccessPw6</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C81" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="inlineStr"/>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr">
-        <is>
-          <t>Message: ICD_Response</t>
-        </is>
-      </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x501</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ICD</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MuxID</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J85" s="3" t="n"/>
-      <c r="K85" s="3" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Tchip</t>
-        </is>
-      </c>
-      <c r="B86" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C86" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F86" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G86" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" s="3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>Resp_AhCounter</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>-2147483648</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>2147483647</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>mAs</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>Resp_OpMode</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>Resp_AccessMode</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Averaging</t>
-        </is>
-      </c>
-      <c r="B90" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C90" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J90" s="3" t="n"/>
-      <c r="K90" s="3" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="3" t="inlineStr">
-        <is>
-          <t>Resp_OCLimitPos</t>
-        </is>
-      </c>
-      <c r="B91" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C91" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K91" s="3" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Resp_CanBaudrate</t>
-        </is>
-      </c>
-      <c r="B92" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C92" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F92" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="3" t="n"/>
-      <c r="K92" s="3" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="3" t="inlineStr">
-        <is>
-          <t>Resp_CanIdReq_SN</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C93" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>Resp_CanIdResp_SN</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J94" s="3" t="n"/>
-      <c r="K94" s="3" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>Resp_CanIdRes_SN</t>
-        </is>
-      </c>
-      <c r="B95" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C95" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F95" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J95" s="3" t="n"/>
-      <c r="K95" s="3" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Pw1</t>
-        </is>
-      </c>
-      <c r="B96" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C96" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J96" s="3" t="n"/>
-      <c r="K96" s="3" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>Resp_ResetOption</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C97" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F97" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I97" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J97" s="3" t="n"/>
-      <c r="K97" s="3" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>Resp_WakeTimer</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C98" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F98" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J98" s="3" t="n"/>
-      <c r="K98" s="3" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
-        <is>
-          <t>Resp_DevId_Frame</t>
-        </is>
-      </c>
-      <c r="B99" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C99" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F99" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J99" s="3" t="n"/>
-      <c r="K99" s="3" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="inlineStr">
-        <is>
-          <t>Resp_FwMajor</t>
-        </is>
-      </c>
-      <c r="B100" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C100" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="H100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J100" s="3" t="n"/>
-      <c r="K100" s="3" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SerialNumber</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C101" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3" t="n">
-        <v>4294967295</v>
-      </c>
-      <c r="J101" s="3" t="n"/>
-      <c r="K101" s="3" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>Resp_HwVer_Frame</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C102" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F102" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" s="3" t="n"/>
-      <c r="K102" s="3" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>Resp_ArticleNumber</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C103" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F103" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="3" t="n">
-        <v>7.2057594038e+16</v>
-      </c>
-      <c r="J103" s="3" t="n"/>
-      <c r="K103" s="3" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>Resp_UpTime</t>
-        </is>
-      </c>
-      <c r="B104" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C104" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F104" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="3" t="n">
-        <v>4294967295</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="K104" s="3" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Lifetime</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="3" t="n">
-        <v>4294967295</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>min</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>Resp_EvtMeasType</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J106" s="3" t="n"/>
-      <c r="K106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>Resp_WakeIThreshold</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="3" t="n"/>
-      <c r="K107" s="3" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>Resp_WakeAhThreshold</t>
-        </is>
-      </c>
-      <c r="B108" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="C108" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F108" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J108" s="3" t="n"/>
-      <c r="K108" s="3" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
-        <is>
-          <t>Resp_OpOutputRate</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C109" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F109" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="3" t="n">
-        <v>65535</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
-      <c r="K109" s="3" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
-        <is>
-          <t>Resp_CanMode</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C110" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J110" s="3" t="n"/>
-      <c r="K110" s="3" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Pw2</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C111" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F111" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I111" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J111" s="3" t="n"/>
-      <c r="K111" s="3" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SleepTimer</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C112" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F112" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="3" t="n">
-        <v>65000</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="K112" s="3" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>Resp_DevId_Char1</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C113" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F113" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J113" s="3" t="n"/>
-      <c r="K113" s="3" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>Resp_FwMinor</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C114" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F114" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G114" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="H114" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J114" s="3" t="n"/>
-      <c r="K114" s="3" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
-        <is>
-          <t>Resp_HwVer_Char1</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C115" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F115" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J115" s="3" t="n"/>
-      <c r="K115" s="3" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
-        <is>
-          <t>Resp_EvtSysType</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C116" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F116" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J116" s="3" t="n"/>
-      <c r="K116" s="3" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Text</t>
-        </is>
-      </c>
-      <c r="B117" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="C117" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F117" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G117" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" s="3" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I117" s="3" t="n">
-        <v>125</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>degC</t>
-        </is>
-      </c>
-      <c r="K117" s="3" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Pw3</t>
-        </is>
-      </c>
-      <c r="B118" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C118" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F118" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G118" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I118" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J118" s="3" t="n"/>
-      <c r="K118" s="3" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
-        <is>
-          <t>Resp_DevId_Char2</t>
-        </is>
-      </c>
-      <c r="B119" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C119" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F119" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J119" s="3" t="n"/>
-      <c r="K119" s="3" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>Resp_FwRelease</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="H120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J120" s="3" t="n"/>
-      <c r="K120" s="3" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>Resp_HwVer_Char2</t>
-        </is>
-      </c>
-      <c r="B121" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C121" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F121" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G121" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H121" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J121" s="3" t="n"/>
-      <c r="K121" s="3" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_CalibrationData</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J122" s="3" t="n"/>
-      <c r="K122" s="3" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>Resp_EvtMeasCount</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="3" t="n">
-        <v>65535</v>
-      </c>
-      <c r="J123" s="3" t="n"/>
-      <c r="K123" s="3" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_OCSActive</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J124" s="3" t="n"/>
-      <c r="K124" s="3" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>Resp_OpInvertCurrent</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C125" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F125" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="3" t="n"/>
-      <c r="K125" s="3" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
-        <is>
-          <t>Resp_OCLimitNeg</t>
-        </is>
-      </c>
-      <c r="B126" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C126" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F126" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="3" t="n">
-        <v>16777215</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>Resp_CanIdReq_ID</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C127" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F127" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="3" t="n">
-        <v>536870911</v>
-      </c>
-      <c r="J127" s="3" t="n"/>
-      <c r="K127" s="3" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="3" t="inlineStr">
-        <is>
-          <t>Resp_CanIdResp_ID</t>
-        </is>
-      </c>
-      <c r="B128" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C128" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F128" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="3" t="n">
-        <v>536870911</v>
-      </c>
-      <c r="J128" s="3" t="n"/>
-      <c r="K128" s="3" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>Resp_CanIdRes_ID</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="3" t="n">
-        <v>536870911</v>
-      </c>
-      <c r="J129" s="3" t="n"/>
-      <c r="K129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Pw4</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C130" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F130" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I130" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J130" s="3" t="n"/>
-      <c r="K130" s="3" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SleepIThreshold</t>
-        </is>
-      </c>
-      <c r="B131" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C131" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F131" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G131" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="3" t="n">
-        <v>250</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>mA</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>Resp_DevId_Char3</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C132" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F132" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J132" s="3" t="n"/>
-      <c r="K132" s="3" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>Resp_HwVer_Char3</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C133" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J133" s="3" t="n"/>
-      <c r="K133" s="3" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Rev_Digit1</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="H134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J134" s="3" t="n"/>
-      <c r="K134" s="3" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_AdcInterrupt</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C135" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J135" s="3" t="n"/>
-      <c r="K135" s="3" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_OverflowAdcCh1</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="n">
-        <v>33</v>
-      </c>
-      <c r="C136" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F136" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J136" s="3" t="n"/>
-      <c r="K136" s="3" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_OverflowAdcCh2</t>
-        </is>
-      </c>
-      <c r="B137" s="3" t="n">
-        <v>34</v>
-      </c>
-      <c r="C137" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F137" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G137" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J137" s="3" t="n"/>
-      <c r="K137" s="3" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_OverflowAdcCh3</t>
-        </is>
-      </c>
-      <c r="B138" s="3" t="n">
-        <v>35</v>
-      </c>
-      <c r="C138" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F138" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G138" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J138" s="3" t="n"/>
-      <c r="K138" s="3" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_OpenCircuitI</t>
-        </is>
-      </c>
-      <c r="B139" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="C139" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F139" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J139" s="3" t="n"/>
-      <c r="K139" s="3" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_OpenCircuitU</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="n">
-        <v>37</v>
-      </c>
-      <c r="C140" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F140" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G140" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J140" s="3" t="n"/>
-      <c r="K140" s="3" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_OpenCircuitTchip</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="n">
-        <v>38</v>
-      </c>
-      <c r="C141" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F141" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H141" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J141" s="3" t="n"/>
-      <c r="K141" s="3" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
-        <is>
-          <t>Resp_MS_OpenCircuitText</t>
-        </is>
-      </c>
-      <c r="B142" s="3" t="n">
-        <v>39</v>
-      </c>
-      <c r="C142" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F142" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G142" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H142" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" s="3" t="n"/>
-      <c r="K142" s="3" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Pw5</t>
-        </is>
-      </c>
-      <c r="B143" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C143" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F143" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I143" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J143" s="3" t="n"/>
-      <c r="K143" s="3" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="3" t="inlineStr">
-        <is>
-          <t>Resp_DevId_Char4</t>
-        </is>
-      </c>
-      <c r="B144" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C144" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F144" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H144" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J144" s="3" t="n"/>
-      <c r="K144" s="3" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="3" t="inlineStr">
-        <is>
-          <t>Resp_HwVer_Char4</t>
-        </is>
-      </c>
-      <c r="B145" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C145" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F145" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G145" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H145" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J145" s="3" t="n"/>
-      <c r="K145" s="3" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Rev_Digit2</t>
-        </is>
-      </c>
-      <c r="B146" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C146" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F146" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G146" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="H146" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J146" s="3" t="n"/>
-      <c r="K146" s="3" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_SystemInit</t>
-        </is>
-      </c>
-      <c r="B147" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C147" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F147" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G147" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H147" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" s="3" t="n"/>
-      <c r="K147" s="3" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>Resp_EvtSysCount</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="C148" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F148" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G148" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H148" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" s="3" t="n">
-        <v>65535</v>
-      </c>
-      <c r="J148" s="3" t="n"/>
-      <c r="K148" s="3" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_Configuration</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="C149" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F149" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G149" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H149" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J149" s="3" t="n"/>
-      <c r="K149" s="3" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_EepromRW</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="n">
-        <v>42</v>
-      </c>
-      <c r="C150" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F150" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G150" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H150" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I150" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J150" s="3" t="n"/>
-      <c r="K150" s="3" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_PowerOnReset</t>
-        </is>
-      </c>
-      <c r="B151" s="3" t="n">
-        <v>43</v>
-      </c>
-      <c r="C151" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F151" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G151" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H151" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I151" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J151" s="3" t="n"/>
-      <c r="K151" s="3" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_LowVoltageReset</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="n">
-        <v>44</v>
-      </c>
-      <c r="C152" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F152" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H152" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J152" s="3" t="n"/>
-      <c r="K152" s="3" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_ExtPinReset</t>
-        </is>
-      </c>
-      <c r="B153" s="3" t="n">
-        <v>45</v>
-      </c>
-      <c r="C153" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F153" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="3" t="n"/>
-      <c r="K153" s="3" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_ClockMonReset</t>
-        </is>
-      </c>
-      <c r="B154" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="C154" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F154" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G154" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H154" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J154" s="3" t="n"/>
-      <c r="K154" s="3" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_CopWdReset</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="n">
-        <v>47</v>
-      </c>
-      <c r="C155" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F155" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G155" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H155" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="3" t="n"/>
-      <c r="K155" s="3" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Pw6</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C156" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F156" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G156" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H156" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="I156" s="3" t="n">
-        <v>126</v>
-      </c>
-      <c r="J156" s="3" t="n"/>
-      <c r="K156" s="3" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SleepAhThreshold</t>
-        </is>
-      </c>
-      <c r="B157" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="C157" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F157" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H157" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" s="3" t="n">
-        <v>65000</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>mAs</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="inlineStr">
-        <is>
-          <t>Resp_DevId_Char5</t>
-        </is>
-      </c>
-      <c r="B158" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C158" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F158" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G158" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I158" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J158" s="3" t="n"/>
-      <c r="K158" s="3" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
-        <is>
-          <t>Resp_HwVer_Char5</t>
-        </is>
-      </c>
-      <c r="B159" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C159" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F159" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H159" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J159" s="3" t="n"/>
-      <c r="K159" s="3" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Rev_Digit3</t>
-        </is>
-      </c>
-      <c r="B160" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C160" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F160" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="H160" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J160" s="3" t="n"/>
-      <c r="K160" s="3" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_CodeCrc</t>
-        </is>
-      </c>
-      <c r="B161" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C161" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F161" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G161" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H161" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J161" s="3" t="n"/>
-      <c r="K161" s="3" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_CalDataCrc</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="n">
-        <v>49</v>
-      </c>
-      <c r="C162" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F162" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G162" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H162" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J162" s="3" t="n"/>
-      <c r="K162" s="3" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_CanRx</t>
-        </is>
-      </c>
-      <c r="B163" s="3" t="n">
-        <v>50</v>
-      </c>
-      <c r="C163" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F163" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G163" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J163" s="3" t="n"/>
-      <c r="K163" s="3" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_CanTx</t>
-        </is>
-      </c>
-      <c r="B164" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="C164" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F164" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H164" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J164" s="3" t="n"/>
-      <c r="K164" s="3" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_Overtemp</t>
-        </is>
-      </c>
-      <c r="B165" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="C165" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F165" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G165" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" s="3" t="n"/>
-      <c r="K165" s="3" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_Undertemp</t>
-        </is>
-      </c>
-      <c r="B166" s="3" t="n">
-        <v>53</v>
-      </c>
-      <c r="C166" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F166" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G166" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H166" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J166" s="3" t="n"/>
-      <c r="K166" s="3" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_PowerFailure</t>
-        </is>
-      </c>
-      <c r="B167" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="C167" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F167" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H167" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J167" s="3" t="n"/>
-      <c r="K167" s="3" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="inlineStr">
-        <is>
-          <t>Resp_SS_SystemClock</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="n">
-        <v>55</v>
-      </c>
-      <c r="C168" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F168" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G168" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H168" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I168" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J168" s="3" t="n"/>
-      <c r="K168" s="3" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="inlineStr">
-        <is>
-          <t>Resp_HwVer_Char6</t>
-        </is>
-      </c>
-      <c r="B169" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C169" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F169" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G169" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H169" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I169" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J169" s="3" t="n"/>
-      <c r="K169" s="3" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="inlineStr">
-        <is>
-          <t>Resp_Rev_Digit4</t>
-        </is>
-      </c>
-      <c r="B170" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C170" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F170" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G170" s="3" t="n">
-        <v>-48</v>
-      </c>
-      <c r="H170" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I170" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="J170" s="3" t="n"/>
-      <c r="K170" s="3" t="inlineStr"/>
-    </row>
-    <row r="171"/>
-    <row r="172">
-      <c r="A172" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT1</t>
-        </is>
-      </c>
-      <c r="B172" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x700</t>
-        </is>
-      </c>
-      <c r="C172" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board1</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="inlineStr">
-        <is>
-          <t>Throtle_Percentage</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C174" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F174" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G174" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H174" s="3" t="n"/>
-      <c r="I174" s="3" t="n"/>
-      <c r="J174" s="3" t="n"/>
-      <c r="K174" s="3" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:K239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13871,7 +7973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25340,7 +19442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29546,7 +23648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -66989,7 +61091,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FSIC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="handcart_t26" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="autonomous_t26" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="powertrain_t26" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="aquisition_boards" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="data_t26" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FSIC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="handcart_t26" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="autonomous_t26" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="powertrain_t26" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="aquisition_boards" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,6 +442,5938 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K175"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT2</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x720</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Acquisition_Board2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>FRONT_LEFT_WHEEL_RPM</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="n"/>
+      <c r="I3" s="3" t="n"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>FRONT_RIGHT_WHEEL_RPM</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="n"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr"/>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT7</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x770</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Acquisition_Board7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>SUSP_L</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n"/>
+      <c r="I8" s="3" t="n"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>SUSP_R</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>NTC_1</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n"/>
+      <c r="I10" s="3" t="n"/>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT8</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x780</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Acquisition_Board8</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>NTC1</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>NTC2</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="n"/>
+      <c r="I15" s="3" t="n"/>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>NTC3</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
+      <c r="I16" s="3" t="n"/>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_INV1_Temperatures</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x444</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>INV1_TempInverter</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>INV1_TempMotor</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_INV2_Temperatures</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x445</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>INV2_TempInverter</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>INV2_TempMotor</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>-55</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>ºC</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Message: PDM_LV</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x210</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): PDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>LV_Voltage_mV</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3" t="n"/>
+      <c r="I30" s="3" t="n"/>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Message: PDM_Cooling</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x220</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): PDM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>WaterPump_PWM</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="n"/>
+      <c r="K34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>CoolingFan_PWM</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="n"/>
+      <c r="K35" s="3" t="inlineStr"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Message: ICD_Result</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x502</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ICD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>ICD_Status_OCS</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="3" t="n"/>
+      <c r="K39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>ICD_Status_MeasError</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="3" t="n"/>
+      <c r="K40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>ICD_Status_SysError</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>ICD_MsgCounter</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J42" s="3" t="n"/>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>ICD_Current</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>ICD_Ubat</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>65.535</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Message: ICD_Request</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x500</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): BMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Req_MuxID</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Req_OpMode</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J49" s="3" t="n"/>
+      <c r="K49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Req_AccessMode</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Req_Averaging</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Req_OCLimitPos</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Req_CanBaudrate</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" s="3" t="n"/>
+      <c r="K53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Req_CanIdReq_SN</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J54" s="3" t="n"/>
+      <c r="K54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Req_CanIdResp_SN</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J55" s="3" t="n"/>
+      <c r="K55" s="3" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Req_CanIdRes_SN</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J56" s="3" t="n"/>
+      <c r="K56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Req_NewPw1</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J57" s="3" t="n"/>
+      <c r="K57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Req_ResetOption</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" s="3" t="n"/>
+      <c r="K58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Req_WakeTimer</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="3" t="n"/>
+      <c r="K59" s="3" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Req_WakeIThreshold</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="n"/>
+      <c r="K60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Req_WakeAhThreshold</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="3" t="n"/>
+      <c r="K61" s="3" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Req_OpOutputRate</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>65535</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Req_AccessPw1</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J63" s="3" t="n"/>
+      <c r="K63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Req_CanMode</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" s="3" t="n"/>
+      <c r="K64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Req_NewPw2</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Req_SleepTimer</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Req_AccessPw2</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Req_NewPw3</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Req_OpInvertCurrent</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Req_AccessPw3</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Req_OCLimitNeg</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Req_CanIdReq_ID</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>536870911</v>
+      </c>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Req_CanIdResp_ID</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>536870911</v>
+      </c>
+      <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Req_CanIdRes_ID</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>536870911</v>
+      </c>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Req_NewPw4</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J75" s="3" t="n"/>
+      <c r="K75" s="3" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Req_SleepIThreshold</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>mA</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>Req_AccessPw4</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J77" s="3" t="n"/>
+      <c r="K77" s="3" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>Req_NewPw5</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>Req_AccessPw5</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Req_NewPw6</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>Req_SleepAhThreshold</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
+        <is>
+          <t>mAs</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Req_AccessPw6</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J82" s="3" t="n"/>
+      <c r="K82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83"/>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>Message: ICD_Response</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x501</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ICD</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MuxID</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Tchip</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>Resp_AhCounter</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>-2147483648</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>2147483647</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>mAs</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Resp_OpMode</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" s="3" t="n"/>
+      <c r="K89" s="3" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>Resp_AccessMode</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" s="3" t="n"/>
+      <c r="K90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Averaging</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J91" s="3" t="n"/>
+      <c r="K91" s="3" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>Resp_OCLimitPos</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Resp_CanBaudrate</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J93" s="3" t="n"/>
+      <c r="K93" s="3" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Resp_CanIdReq_SN</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Resp_CanIdResp_SN</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>Resp_CanIdRes_SN</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Pw1</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J97" s="3" t="n"/>
+      <c r="K97" s="3" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Resp_ResetOption</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C98" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J98" s="3" t="n"/>
+      <c r="K98" s="3" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Resp_WakeTimer</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="3" t="n"/>
+      <c r="K99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Resp_DevId_Frame</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>Resp_FwMajor</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J101" s="3" t="n"/>
+      <c r="K101" s="3" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SerialNumber</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3" t="n">
+        <v>4294967295</v>
+      </c>
+      <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>Resp_HwVer_Frame</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="3" t="n"/>
+      <c r="K103" s="3" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Resp_ArticleNumber</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>7.2057594038e+16</v>
+      </c>
+      <c r="J104" s="3" t="n"/>
+      <c r="K104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>Resp_UpTime</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="3" t="n">
+        <v>4294967295</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Lifetime</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="3" t="n">
+        <v>4294967295</v>
+      </c>
+      <c r="J106" s="3" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Resp_EvtMeasType</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J107" s="3" t="n"/>
+      <c r="K107" s="3" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Resp_WakeIThreshold</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J108" s="3" t="n"/>
+      <c r="K108" s="3" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Resp_WakeAhThreshold</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="3" t="n"/>
+      <c r="K109" s="3" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>Resp_OpOutputRate</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="3" t="n">
+        <v>65535</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>ms</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>Resp_CanMode</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Pw2</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F112" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I112" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SleepTimer</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>Resp_DevId_Char1</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J114" s="3" t="n"/>
+      <c r="K114" s="3" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Resp_FwMinor</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>Resp_HwVer_Char1</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Resp_EvtSysType</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Text</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F118" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="3" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I118" s="3" t="n">
+        <v>125</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Pw3</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F119" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I119" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>Resp_DevId_Char2</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F120" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>Resp_FwRelease</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F121" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J121" s="3" t="n"/>
+      <c r="K121" s="3" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>Resp_HwVer_Char2</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F122" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J122" s="3" t="n"/>
+      <c r="K122" s="3" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_CalibrationData</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Resp_EvtMeasCount</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="3" t="n">
+        <v>65535</v>
+      </c>
+      <c r="J124" s="3" t="n"/>
+      <c r="K124" s="3" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_OCSActive</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>Resp_OpInvertCurrent</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J126" s="3" t="n"/>
+      <c r="K126" s="3" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Resp_OCLimitNeg</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="3" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Resp_CanIdReq_ID</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="3" t="n">
+        <v>536870911</v>
+      </c>
+      <c r="J128" s="3" t="n"/>
+      <c r="K128" s="3" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>Resp_CanIdResp_ID</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="3" t="n">
+        <v>536870911</v>
+      </c>
+      <c r="J129" s="3" t="n"/>
+      <c r="K129" s="3" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Resp_CanIdRes_ID</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F130" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>536870911</v>
+      </c>
+      <c r="J130" s="3" t="n"/>
+      <c r="K130" s="3" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Pw4</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J131" s="3" t="n"/>
+      <c r="K131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SleepIThreshold</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>250</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>mA</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Resp_DevId_Char3</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J133" s="3" t="n"/>
+      <c r="K133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>Resp_HwVer_Char3</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F134" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J134" s="3" t="n"/>
+      <c r="K134" s="3" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Rev_Digit1</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J135" s="3" t="n"/>
+      <c r="K135" s="3" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_AdcInterrupt</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C136" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F136" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_OverflowAdcCh1</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_OverflowAdcCh2</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_OverflowAdcCh3</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" s="3" t="n"/>
+      <c r="K139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_OpenCircuitI</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="C140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J140" s="3" t="n"/>
+      <c r="K140" s="3" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_OpenCircuitU</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="C141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_OpenCircuitTchip</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="C142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Resp_MS_OpenCircuitText</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="3" t="n"/>
+      <c r="K143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Pw5</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I144" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J144" s="3" t="n"/>
+      <c r="K144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>Resp_DevId_Char4</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C145" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F145" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J145" s="3" t="n"/>
+      <c r="K145" s="3" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Resp_HwVer_Char4</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C146" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F146" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J146" s="3" t="n"/>
+      <c r="K146" s="3" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Rev_Digit2</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C147" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F147" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G147" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H147" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J147" s="3" t="n"/>
+      <c r="K147" s="3" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_SystemInit</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" s="3" t="n"/>
+      <c r="K148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr">
+        <is>
+          <t>Resp_EvtSysCount</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C149" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F149" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" s="3" t="n">
+        <v>65535</v>
+      </c>
+      <c r="J149" s="3" t="n"/>
+      <c r="K149" s="3" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_Configuration</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="C150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" s="3" t="n"/>
+      <c r="K150" s="3" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_EepromRW</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="C151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="3" t="n"/>
+      <c r="K151" s="3" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_PowerOnReset</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_LowVoltageReset</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_ExtPinReset</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_ClockMonReset</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="3" t="n"/>
+      <c r="K155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_CopWdReset</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="C156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" s="3" t="n"/>
+      <c r="K156" s="3" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Pw6</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C157" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F157" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I157" s="3" t="n">
+        <v>126</v>
+      </c>
+      <c r="J157" s="3" t="n"/>
+      <c r="K157" s="3" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SleepAhThreshold</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C158" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F158" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="3" t="n">
+        <v>65000</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>mAs</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Resp_DevId_Char5</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Resp_HwVer_Char5</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Rev_Digit3</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J161" s="3" t="n"/>
+      <c r="K161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_CodeCrc</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="3" t="n"/>
+      <c r="K162" s="3" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_CalDataCrc</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="C163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="3" t="n"/>
+      <c r="K163" s="3" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_CanRx</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="C164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="3" t="n"/>
+      <c r="K164" s="3" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_CanTx</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" s="3" t="n"/>
+      <c r="K165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_Overtemp</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" s="3" t="n"/>
+      <c r="K166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_Undertemp</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" s="3" t="n"/>
+      <c r="K167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_PowerFailure</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="C168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I168" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J168" s="3" t="n"/>
+      <c r="K168" s="3" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="inlineStr">
+        <is>
+          <t>Resp_SS_SystemClock</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="C169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I169" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" s="3" t="n"/>
+      <c r="K169" s="3" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>Resp_HwVer_Char6</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C170" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F170" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I170" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J170" s="3" t="n"/>
+      <c r="K170" s="3" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Resp_Rev_Digit4</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172"/>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>Message: AQT1</t>
+        </is>
+      </c>
+      <c r="B173" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x700</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): Acquisition_Board1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>Throtle_Percentage</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="3" t="n"/>
+      <c r="I175" s="3" t="n"/>
+      <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7973,7 +13906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -19442,7 +25375,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23648,7 +29581,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -61091,7 +67024,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -25381,7 +25381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -26358,17 +26358,17 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>Message: AQT2</t>
+          <t>Message: AQT4</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x720</t>
+          <t>ID: 0x740</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): Acquisition_Board2</t>
+          <t>Sender(s): Acquisition_Board4</t>
         </is>
       </c>
     </row>
@@ -26432,7 +26432,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>WHEEL_SPD</t>
+          <t>ST_ANGLE</t>
         </is>
       </c>
       <c r="B33" s="3" t="n">
@@ -26459,97 +26459,123 @@
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>ms</t>
+          <t>Âº</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr"/>
     </row>
-    <row r="34"/>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>SUSP_L</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3" t="n"/>
+      <c r="I34" s="3" t="n"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr"/>
+    </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT3</t>
-        </is>
-      </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x730</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board3</t>
-        </is>
-      </c>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>SUSP_R</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n"/>
+      <c r="I35" s="3" t="n"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>INERTIA</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3" t="n"/>
+      <c r="I36" s="3" t="n"/>
+      <c r="J36" s="3" t="n"/>
+      <c r="K36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>WHEEL_SPD</t>
+          <t>EMERGENCY</t>
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
@@ -26557,38 +26583,34 @@
         </is>
       </c>
       <c r="E37" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>ms</t>
-        </is>
-      </c>
+      <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr"/>
     </row>
     <row r="38"/>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Message: AQT4</t>
+          <t>Message: AQT7</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x740</t>
+          <t>ID: 0x770</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): Acquisition_Board4</t>
+          <t>Sender(s): Acquisition_Board7</t>
         </is>
       </c>
     </row>
@@ -26652,7 +26674,7 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ST_ANGLE</t>
+          <t>REAR_BRK_PRESS</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
@@ -26667,7 +26689,7 @@
         </is>
       </c>
       <c r="E41" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3" t="n">
         <v>0.1</v>
@@ -26679,123 +26701,97 @@
       <c r="I41" s="3" t="n"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>Âº</t>
+          <t>bar</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr"/>
     </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>SUSP_L</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="K42" s="3" t="inlineStr"/>
-    </row>
+    <row r="42"/>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>SUSP_R</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_IGN_R2D</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x600</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>INERTIA</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="inlineStr"/>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>EMERGENCY</t>
+          <t>ignition_manual</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
@@ -26816,92 +26812,110 @@
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr"/>
     </row>
-    <row r="46"/>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>r2d_manual</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="3" t="n"/>
+      <c r="I46" s="3" t="n"/>
+      <c r="J46" s="3" t="n"/>
+      <c r="K46" s="3" t="inlineStr"/>
+    </row>
     <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>Message: AQT7</t>
-        </is>
-      </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x770</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): Acquisition_Board7</t>
-        </is>
-      </c>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>ignition_auto</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="3" t="n"/>
+      <c r="I47" s="3" t="n"/>
+      <c r="J47" s="3" t="n"/>
+      <c r="K47" s="3" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>r2d_auto</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="3" t="n"/>
+      <c r="I48" s="3" t="n"/>
+      <c r="J48" s="3" t="n"/>
+      <c r="K48" s="3" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>REAR_BRK_PRESS</t>
+          <t>shutdown_signal</t>
         </is>
       </c>
       <c r="B49" s="3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
@@ -26912,196 +26926,192 @@
         <v>0</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
+      <c r="J49" s="3" t="n"/>
       <c r="K49" s="3" t="inlineStr"/>
     </row>
-    <row r="50"/>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>vcu_state</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3" t="n"/>
+      <c r="I50" s="3" t="n"/>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="inlineStr"/>
+    </row>
     <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_IGN_R2D</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x600</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>R2D_button_raw</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="3" t="n"/>
+      <c r="I51" s="3" t="n"/>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Ignition_switch_raw</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3" t="n"/>
+      <c r="I52" s="3" t="n"/>
+      <c r="J52" s="3" t="n"/>
+      <c r="K52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_1</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x500</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="I55" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
+      <c r="J55" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K55" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>ignition_manual</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
-      <c r="J53" s="3" t="n"/>
-      <c r="K53" s="3" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>r2d_manual</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C54" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="3" t="n"/>
-      <c r="K54" s="3" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>ignition_auto</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C55" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
-      <c r="J55" s="3" t="n"/>
-      <c r="K55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>r2d_auto</t>
+          <t>Speed_actual</t>
         </is>
       </c>
       <c r="B56" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C56" s="3" t="n">
         <v>8</v>
@@ -27120,19 +27130,27 @@
       <c r="G56" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H56" s="3" t="n"/>
-      <c r="I56" s="3" t="n"/>
-      <c r="J56" s="3" t="n"/>
+      <c r="H56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
       <c r="K56" s="3" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>shutdown_signal</t>
+          <t>Speed_target</t>
         </is>
       </c>
       <c r="B57" s="3" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C57" s="3" t="n">
         <v>8</v>
@@ -27151,19 +27169,27 @@
       <c r="G57" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
-      <c r="J57" s="3" t="n"/>
+      <c r="H57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>km/h</t>
+        </is>
+      </c>
       <c r="K57" s="3" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>vcu_state</t>
+          <t>Steering_angle_actual</t>
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="C58" s="3" t="n">
         <v>8</v>
@@ -27174,27 +27200,35 @@
         </is>
       </c>
       <c r="E58" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
-      <c r="J58" s="3" t="n"/>
+      <c r="H58" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
       <c r="K58" s="3" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>R2D_button_raw</t>
+          <t>Steering_angle_target</t>
         </is>
       </c>
       <c r="B59" s="3" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C59" s="3" t="n">
         <v>8</v>
@@ -27205,27 +27239,35 @@
         </is>
       </c>
       <c r="E59" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="3" t="n"/>
-      <c r="I59" s="3" t="n"/>
-      <c r="J59" s="3" t="n"/>
+      <c r="H59" s="3" t="n">
+        <v>-64</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
       <c r="K59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Ignition_switch_raw</t>
+          <t>Brake_hydr_actual</t>
         </is>
       </c>
       <c r="B60" s="3" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C60" s="3" t="n">
         <v>8</v>
@@ -27244,214 +27286,222 @@
       <c r="G60" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
-      <c r="J60" s="3" t="n"/>
+      <c r="H60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
       <c r="K60" s="3" t="inlineStr"/>
     </row>
-    <row r="61"/>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Brake_hydr_target</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr"/>
+    </row>
     <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_dynamics_1</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x500</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_actual</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Motor_moment_target</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>-128</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>127</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr"/>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_dynamics_2</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x501</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>Sender(s): JETSON</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
+      <c r="J66" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K66" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>Speed_actual</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Speed_target</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C65" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>km/h</t>
-        </is>
-      </c>
-      <c r="K65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>Steering_angle_actual</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C66" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>rad</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Steering_angle_target</t>
+          <t>Acceleration_longitudinal</t>
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
@@ -27462,20 +27512,16 @@
         <v>1</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.5</v>
+        <v>0.001953125</v>
       </c>
       <c r="G67" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H67" s="3" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>63.5</v>
-      </c>
+      <c r="H67" s="3" t="n"/>
+      <c r="I67" s="3" t="n"/>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>rad</t>
+          <t>m/s2</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr"/>
@@ -27483,14 +27529,14 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>Brake_hydr_actual</t>
+          <t>Acceleration_lateral</t>
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
@@ -27498,23 +27544,19 @@
         </is>
       </c>
       <c r="E68" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1</v>
+        <v>0.001953125</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="n"/>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>m/s2</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr"/>
@@ -27522,206 +27564,186 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>Brake_hydr_target</t>
+          <t>Yaw_rate</t>
         </is>
       </c>
       <c r="B69" s="3" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C69" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>0.0078125</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>m/s2</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70"/>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_HV</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x81</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>HV</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E69" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>Motor_moment_actual</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="n">
-        <v>48</v>
-      </c>
-      <c r="C70" s="3" t="n">
+      <c r="E73" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="3" t="n"/>
+      <c r="I73" s="3" t="n"/>
+      <c r="J73" s="3" t="n"/>
+      <c r="K73" s="3" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Brake_pressure_Front</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="C74" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E70" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="3" t="n">
-        <v>-128</v>
-      </c>
-      <c r="I70" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Motor_moment_target</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="n">
-        <v>56</v>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>-128</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr"/>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_dynamics_2</t>
-        </is>
-      </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x501</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="E74" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="n"/>
+      <c r="K74" s="3" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>Acceleration_longitudinal</t>
+          <t>Brake_pressure_Rear</t>
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
@@ -27729,179 +27751,183 @@
         </is>
       </c>
       <c r="E75" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.001953125</v>
+        <v>1</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
-      <c r="J75" s="3" t="inlineStr">
-        <is>
-          <t>m/s2</t>
-        </is>
-      </c>
+      <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr"/>
     </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>Acceleration_lateral</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C76" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
+    <row r="76"/>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>Message: DV_status</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x502</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): ACU</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>AS_status</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E76" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>0.001953125</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="3" t="n"/>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>m/s2</t>
-        </is>
-      </c>
-      <c r="K76" s="3" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>Yaw_rate</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C77" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="E79" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>1=AS_status_off, 2=AS_status_ready, 3=AS_status_driving, 4=AS_status_emergency, 5=AS_status_finished</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>ASB_EBS_state</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E77" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>0.0078125</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" s="3" t="n"/>
-      <c r="I77" s="3" t="n"/>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>m/s2</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr"/>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_HV</t>
-        </is>
-      </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x81</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
+      <c r="E80" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_EBS_state_deactivated, 2=ASB_EBS_state_initial_checkup_passed, 3=ASB_EBS_state_activated</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>HV</t>
+          <t>AMI_state</t>
         </is>
       </c>
       <c r="B81" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C81" s="3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
@@ -27917,22 +27943,30 @@
       <c r="G81" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
+      <c r="H81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="inlineStr"/>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>1=AMI_state_acceleration, 2=AMI_state_skidpad, 3=AMI_state_trackdrive, 4=AMI_state_braketest, 5=AMI_state_inspection, 6=AMI_state_autocross</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Brake_pressure_Front</t>
+          <t>Steering_state</t>
         </is>
       </c>
       <c r="B82" s="3" t="n">
         <v>8</v>
       </c>
       <c r="C82" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
@@ -27948,246 +27982,246 @@
       <c r="G82" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="3" t="n"/>
-      <c r="I82" s="3" t="n"/>
+      <c r="H82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J82" s="3" t="n"/>
       <c r="K82" s="3" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>Brake_pressure_Rear</t>
+          <t>ASB_redundancy_state</t>
         </is>
       </c>
       <c r="B83" s="3" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>1=ASB_redundancy_state_deactivated, 2=ASB_redundancy_state_engaged, 3=ASB_redundancy_state_initial_checkup_passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Lap_counter</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_actual</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C85" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E83" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="3" t="n"/>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="3" t="inlineStr"/>
-    </row>
-    <row r="84"/>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
-        <is>
-          <t>Message: DV_status</t>
-        </is>
-      </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x502</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="E85" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>255</v>
+      </c>
+      <c r="J85" s="3" t="n"/>
+      <c r="K85" s="3" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_all</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>131071</v>
+      </c>
+      <c r="J86" s="3" t="n"/>
+      <c r="K86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>Message: ASF_SIGNALS</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x511</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t>Sender(s): ACU</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J86" s="2" t="inlineStr">
+      <c r="J89" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="K89" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>AS_status</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>1=AS_status_off, 2=AS_status_ready, 3=AS_status_driving, 4=AS_status_emergency, 5=AS_status_finished</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>ASB_EBS_state</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C88" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" s="3" t="n"/>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>1=ASB_EBS_state_deactivated, 2=ASB_EBS_state_initial_checkup_passed, 3=ASB_EBS_state_activated</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>AMI_state</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="C89" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>1=AMI_state_acceleration, 2=AMI_state_skidpad, 3=AMI_state_trackdrive, 4=AMI_state_braketest, 5=AMI_state_inspection, 6=AMI_state_autocross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>Steering_state</t>
+          <t>EBS_Pressure_Tank_Front</t>
         </is>
       </c>
       <c r="B90" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="C90" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
@@ -28197,31 +28231,31 @@
         <v>0</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G90" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H90" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="3" t="n"/>
+      <c r="H90" s="3" t="n"/>
+      <c r="I90" s="3" t="n"/>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
       <c r="K90" s="3" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>ASB_redundancy_state</t>
+          <t>EBS_Pressure_Tank_Rear</t>
         </is>
       </c>
       <c r="B91" s="3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C91" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
@@ -28232,35 +28266,31 @@
         <v>0</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H91" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J91" s="3" t="n"/>
-      <c r="K91" s="3" t="inlineStr">
-        <is>
-          <t>1=ASB_redundancy_state_deactivated, 2=ASB_redundancy_state_engaged, 3=ASB_redundancy_state_initial_checkup_passed</t>
-        </is>
-      </c>
+      <c r="H91" s="3" t="n"/>
+      <c r="I91" s="3" t="n"/>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>Lap_counter</t>
+          <t>Brake_Pressure_Front</t>
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
@@ -28271,28 +28301,28 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H92" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="J92" s="3" t="n"/>
+      <c r="H92" s="3" t="n"/>
+      <c r="I92" s="3" t="n"/>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
       <c r="K92" s="3" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>Cones_count_actual</t>
+          <t>Brake_Pressure_Rear</t>
         </is>
       </c>
       <c r="B93" s="3" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C93" s="3" t="n">
         <v>8</v>
@@ -28306,141 +28336,145 @@
         <v>0</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G93" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H93" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>255</v>
-      </c>
-      <c r="J93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="I93" s="3" t="n"/>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
       <c r="K93" s="3" t="inlineStr"/>
     </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>Cones_count_all</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="C94" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
+    <row r="94"/>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x509</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): VCU</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>motor_rpm_left</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E94" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>131071</v>
-      </c>
-      <c r="J94" s="3" t="n"/>
-      <c r="K94" s="3" t="inlineStr"/>
-    </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="1" t="inlineStr">
-        <is>
-          <t>Message: ASF_SIGNALS</t>
-        </is>
-      </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x511</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): ACU</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="E97" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
         <is>
-          <t>EBS_Pressure_Tank_Front</t>
+          <t>motor_rpm_right</t>
         </is>
       </c>
       <c r="B98" s="3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C98" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
@@ -28451,7 +28485,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G98" s="3" t="n">
         <v>0</v>
@@ -28460,7 +28494,7 @@
       <c r="I98" s="3" t="n"/>
       <c r="J98" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="K98" s="3" t="inlineStr"/>
@@ -28468,14 +28502,14 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>EBS_Pressure_Tank_Rear</t>
+          <t>motor_current_left</t>
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
@@ -28483,10 +28517,10 @@
         </is>
       </c>
       <c r="E99" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>0</v>
@@ -28495,7 +28529,7 @@
       <c r="I99" s="3" t="n"/>
       <c r="J99" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K99" s="3" t="inlineStr"/>
@@ -28503,14 +28537,14 @@
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
         <is>
-          <t>Brake_Pressure_Front</t>
+          <t>motor_current_right</t>
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
@@ -28518,10 +28552,10 @@
         </is>
       </c>
       <c r="E100" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G100" s="3" t="n">
         <v>0</v>
@@ -28530,238 +28564,208 @@
       <c r="I100" s="3" t="n"/>
       <c r="J100" s="3" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K100" s="3" t="inlineStr"/>
     </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
-        <is>
-          <t>Brake_Pressure_Rear</t>
-        </is>
-      </c>
-      <c r="B101" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C101" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_TORQUE_TARGET</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x49a</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>torque_target</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E101" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="n"/>
-      <c r="I101" s="3" t="n"/>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>bar</t>
-        </is>
-      </c>
-      <c r="K101" s="3" t="inlineStr"/>
-    </row>
-    <row r="102"/>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_RPM</t>
-        </is>
-      </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x509</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): VCU</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="E104" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="3" t="n">
+        <v>-100</v>
+      </c>
+      <c r="I104" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>RPM</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr"/>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>Message: VCU_RPM_TARGET</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x499</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J104" s="2" t="inlineStr">
+      <c r="J107" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
-        <is>
-          <t>motor_rpm_left</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F105" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>motor_rpm_right</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C106" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F106" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="3" t="n"/>
-      <c r="I106" s="3" t="n"/>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>motor_current_left</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="C107" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="3" t="n"/>
-      <c r="I107" s="3" t="n"/>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>motor_current_right</t>
+          <t>rpm_target</t>
         </is>
       </c>
       <c r="B108" s="3" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>16</v>
@@ -28780,11 +28784,15 @@
       <c r="G108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H108" s="3" t="n"/>
-      <c r="I108" s="3" t="n"/>
+      <c r="H108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="3" t="n">
+        <v>6000</v>
+      </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>RPM</t>
         </is>
       </c>
       <c r="K108" s="3" t="inlineStr"/>
@@ -28793,12 +28801,12 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>Message: VCU_TORQUE_TARGET</t>
+          <t>Message: JETSON</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x49a</t>
+          <t>ID: 0x61</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -28867,14 +28875,14 @@
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
         <is>
-          <t>torque_target</t>
+          <t>AS_STATE</t>
         </is>
       </c>
       <c r="B112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
@@ -28882,7 +28890,7 @@
         </is>
       </c>
       <c r="E112" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>1</v>
@@ -28891,104 +28899,130 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J112" s="3" t="n"/>
+      <c r="K112" s="3" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>AS_MISSION</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J113" s="3" t="n"/>
+      <c r="K113" s="3" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>TEMPERATURE</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F114" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
-      <c r="K112" s="3" t="inlineStr"/>
-    </row>
-    <row r="113"/>
-    <row r="114">
-      <c r="A114" s="1" t="inlineStr">
-        <is>
-          <t>Message: VCU_RPM_TARGET</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x499</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
+      <c r="J114" s="3" t="n"/>
+      <c r="K114" s="3" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>CPU</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J115" s="3" t="n"/>
+      <c r="K115" s="3" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>rpm_target</t>
+          <t>GPU</t>
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
@@ -28996,7 +29030,7 @@
         </is>
       </c>
       <c r="E116" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
         <v>1</v>
@@ -29008,136 +29042,132 @@
         <v>0</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>RPM</t>
-        </is>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="J116" s="3" t="n"/>
       <c r="K116" s="3" t="inlineStr"/>
     </row>
-    <row r="117"/>
-    <row r="118">
-      <c r="A118" s="1" t="inlineStr">
-        <is>
-          <t>Message: JETSON</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x61</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>EMERGENCY_CAUSE</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="3" t="n"/>
+      <c r="I117" s="3" t="n"/>
+      <c r="J117" s="3" t="n"/>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>0=None, 1=RES, 2=ACU, 3=ZED, 4=Steering_error, 5=Steering_timeout, 6=Planner, 7=SLAM, 8=P-Puma, 9=IMU</t>
+        </is>
+      </c>
+    </row>
+    <row r="118"/>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>Message: RES</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x191</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): RES</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Signal Name</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Start Bit</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
         <is>
           <t>Length (bits)</t>
         </is>
       </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Byte Order</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Signed</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Factor</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>Offset</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="J119" s="2" t="inlineStr">
+      <c r="J120" s="2" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr">
+      <c r="K120" s="2" t="inlineStr">
         <is>
           <t>Choices</t>
         </is>
       </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>AS_STATE</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F120" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J120" s="3" t="n"/>
-      <c r="K120" s="3" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="3" t="inlineStr">
         <is>
-          <t>AS_MISSION</t>
+          <t>SIGNAL</t>
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
@@ -29153,131 +29183,97 @@
       <c r="G121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="H121" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" s="3" t="n">
-        <v>7</v>
-      </c>
+      <c r="H121" s="3" t="n"/>
+      <c r="I121" s="3" t="n"/>
       <c r="J121" s="3" t="n"/>
       <c r="K121" s="3" t="inlineStr"/>
     </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
-        <is>
-          <t>TEMPERATURE</t>
-        </is>
-      </c>
-      <c r="B122" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C122" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F122" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J122" s="3" t="n"/>
-      <c r="K122" s="3" t="inlineStr"/>
-    </row>
+    <row r="122"/>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr">
-        <is>
-          <t>CPU</t>
-        </is>
-      </c>
-      <c r="B123" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="C123" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F123" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H123" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J123" s="3" t="n"/>
-      <c r="K123" s="3" t="inlineStr"/>
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>Message: SLAM_STATS_CAN</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x505</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>GPU</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="C124" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F124" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H124" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="J124" s="3" t="n"/>
-      <c r="K124" s="3" t="inlineStr"/>
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>EMERGENCY_CAUSE</t>
+          <t>Lap_counter</t>
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
@@ -29296,285 +29292,69 @@
       <c r="H125" s="3" t="n"/>
       <c r="I125" s="3" t="n"/>
       <c r="J125" s="3" t="n"/>
-      <c r="K125" s="3" t="inlineStr">
-        <is>
-          <t>0=None, 1=RES, 2=ACU, 3=ZED, 4=Steering_error, 5=Steering_timeout, 6=Planner, 7=SLAM, 8=P-Puma, 9=IMU</t>
-        </is>
-      </c>
-    </row>
-    <row r="126"/>
+      <c r="K125" s="3" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_actual</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="3" t="n"/>
+      <c r="I126" s="3" t="n"/>
+      <c r="J126" s="3" t="n"/>
+      <c r="K126" s="3" t="inlineStr"/>
+    </row>
     <row r="127">
-      <c r="A127" s="1" t="inlineStr">
-        <is>
-          <t>Message: RES</t>
-        </is>
-      </c>
-      <c r="B127" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x191</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): RES</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="3" t="inlineStr">
-        <is>
-          <t>SIGNAL</t>
-        </is>
-      </c>
-      <c r="B129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>Cones_count_all</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C127" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>Intel</t>
         </is>
       </c>
-      <c r="E129" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F129" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G129" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" s="3" t="n"/>
-      <c r="I129" s="3" t="n"/>
-      <c r="J129" s="3" t="n"/>
-      <c r="K129" s="3" t="inlineStr"/>
-    </row>
-    <row r="130"/>
-    <row r="131">
-      <c r="A131" s="1" t="inlineStr">
-        <is>
-          <t>Message: SLAM_STATS_CAN</t>
-        </is>
-      </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>ID: 0x505</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>Sender(s): JETSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Signal Name</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Start Bit</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Length (bits)</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Byte Order</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Signed</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr">
-        <is>
-          <t>Offset</t>
-        </is>
-      </c>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>Min</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>Max</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="inlineStr">
-        <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>Choices</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="3" t="inlineStr">
-        <is>
-          <t>Lap_counter</t>
-        </is>
-      </c>
-      <c r="B133" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C133" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F133" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G133" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" s="3" t="n"/>
-      <c r="I133" s="3" t="n"/>
-      <c r="J133" s="3" t="n"/>
-      <c r="K133" s="3" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
-        <is>
-          <t>Cones_count_actual</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C134" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F134" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" s="3" t="n"/>
-      <c r="I134" s="3" t="n"/>
-      <c r="J134" s="3" t="n"/>
-      <c r="K134" s="3" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
-        <is>
-          <t>Cones_count_all</t>
-        </is>
-      </c>
-      <c r="B135" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C135" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>Intel</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F135" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G135" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
-      <c r="J135" s="3" t="n"/>
-      <c r="K135" s="3" t="inlineStr"/>
+      <c r="E127" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="3" t="n"/>
+      <c r="I127" s="3" t="n"/>
+      <c r="J127" s="3" t="n"/>
+      <c r="K127" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K175"/>
+  <dimension ref="A1:K182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>Sender(s): BMS</t>
+          <t>Sender(s): PDM</t>
         </is>
       </c>
     </row>
@@ -6362,6 +6362,221 @@
       <c r="I175" s="3" t="n"/>
       <c r="J175" s="3" t="n"/>
       <c r="K175" s="3" t="inlineStr"/>
+    </row>
+    <row r="176"/>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Message: Master_MSC_ID_3</t>
+        </is>
+      </c>
+      <c r="B177" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x750</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): BMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>overall_maximum_voltage</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" s="3" t="n"/>
+      <c r="I179" s="3" t="n"/>
+      <c r="J179" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>overall_maximum_temperature</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="3" t="n"/>
+      <c r="I180" s="3" t="n"/>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>overall_minimum_voltage</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="3" t="n"/>
+      <c r="I181" s="3" t="n"/>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>overall_minimum_temperature</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" s="3" t="n"/>
+      <c r="I182" s="3" t="n"/>
+      <c r="J182" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x720</t>
+          <t>ID: 0x22</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -67945,7 +67945,7 @@
       </c>
       <c r="B938" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x740</t>
+          <t>ID: 0x70</t>
         </is>
       </c>
       <c r="C938" s="1" t="inlineStr">

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -466,7 +466,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>ID: 0x22</t>
+          <t>ID: 0x30</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -34884,7 +34884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K127"/>
+  <dimension ref="A1:K191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -34896,7 +34896,7 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
     <col width="376" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -38858,6 +38858,2070 @@
       <c r="I127" s="3" t="n"/>
       <c r="J127" s="3" t="n"/>
       <c r="K127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128"/>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_Acceleration</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x530</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_X</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F131" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I131" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_Y</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F132" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G132" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I132" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>Acceleration_Z</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F133" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G133" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr"/>
+    </row>
+    <row r="134"/>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_Angular_Velocity</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x531</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Angular_Velocity_X</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C137" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F137" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G137" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>-32.768</v>
+      </c>
+      <c r="I137" s="3" t="n">
+        <v>32.767</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>rad/s</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>Angular_Velocity_Y</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C138" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F138" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G138" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>-32.768</v>
+      </c>
+      <c r="I138" s="3" t="n">
+        <v>32.767</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>rad/s</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Angular_Velocity_Z</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C139" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F139" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G139" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>-32.768</v>
+      </c>
+      <c r="I139" s="3" t="n">
+        <v>32.767</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>rad/s</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr"/>
+    </row>
+    <row r="140"/>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_GNSS_Position</t>
+        </is>
+      </c>
+      <c r="B141" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x532</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C143" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F143" s="3" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="G143" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="I143" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C144" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F144" s="3" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="G144" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" s="3" t="n">
+        <v>-180</v>
+      </c>
+      <c r="I144" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr"/>
+    </row>
+    <row r="145"/>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_GNSS_Altitude</t>
+        </is>
+      </c>
+      <c r="B146" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x533</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Altitude</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C148" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F148" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G148" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" s="3" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="I148" s="3" t="n">
+        <v>10000</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr"/>
+    </row>
+    <row r="149"/>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_Orientation</t>
+        </is>
+      </c>
+      <c r="B150" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x534</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Quaternion_W</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C152" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F152" s="3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G152" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I152" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>Quaternion_X</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C153" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F153" s="3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G153" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I153" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="3" t="n"/>
+      <c r="K153" s="3" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>Quaternion_Y</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C154" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F154" s="3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G154" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I154" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" s="3" t="n"/>
+      <c r="K154" s="3" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>Quaternion_Z</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="C155" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F155" s="3" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="G155" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I155" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="3" t="n"/>
+      <c r="K155" s="3" t="inlineStr"/>
+    </row>
+    <row r="156"/>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_Velocity</t>
+        </is>
+      </c>
+      <c r="B157" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x535</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Velocity_X</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C159" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F159" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G159" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I159" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>Velocity_Y</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C160" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F160" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I160" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Velocity_Z</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C161" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F161" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I161" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr"/>
+    </row>
+    <row r="162"/>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_Euler</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x536</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C165" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F165" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G165" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" s="3" t="n">
+        <v>-180</v>
+      </c>
+      <c r="I165" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="J165" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
+        <is>
+          <t>Pitch</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C166" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F166" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G166" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" s="3" t="n">
+        <v>-90</v>
+      </c>
+      <c r="I166" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
+        <is>
+          <t>Yaw</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C167" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F167" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" s="3" t="n">
+        <v>-180</v>
+      </c>
+      <c r="I167" s="3" t="n">
+        <v>180</v>
+      </c>
+      <c r="J167" s="3" t="inlineStr">
+        <is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr"/>
+    </row>
+    <row r="168"/>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_Status</t>
+        </is>
+      </c>
+      <c r="B169" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x537</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="3" t="inlineStr">
+        <is>
+          <t>Self_Test</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I171" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" s="3" t="n"/>
+      <c r="K171" s="3" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Filter_Valid</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I172" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J172" s="3" t="n"/>
+      <c r="K172" s="3" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>GNSS_Fix</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C173" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F173" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I173" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" s="3" t="n"/>
+      <c r="K173" s="3" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>No_Rotation_Update_Status</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C174" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F174" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I174" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J174" s="3" t="n"/>
+      <c r="K174" s="3" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="3" t="inlineStr">
+        <is>
+          <t>Representative_Motion</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I175" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" s="3" t="n"/>
+      <c r="K175" s="3" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="inlineStr">
+        <is>
+          <t>Clock_Bias_Estimation</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I176" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="3" t="n"/>
+      <c r="K176" s="3" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="inlineStr">
+        <is>
+          <t>Clip_Acc_X</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I177" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="3" t="n"/>
+      <c r="K177" s="3" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>Clip_Acc_Y</t>
+        </is>
+      </c>
+      <c r="B178" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C178" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F178" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I178" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" s="3" t="n"/>
+      <c r="K178" s="3" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>Clip_Acc_Z</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C179" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F179" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" s="3" t="n"/>
+      <c r="K179" s="3" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="3" t="inlineStr">
+        <is>
+          <t>Clip_Gyr_X</t>
+        </is>
+      </c>
+      <c r="B180" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I180" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" s="3" t="n"/>
+      <c r="K180" s="3" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>Clip_Gyr_Y</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="3" t="n"/>
+      <c r="K181" s="3" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
+        <is>
+          <t>Clip_Gyr_Z</t>
+        </is>
+      </c>
+      <c r="B182" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I182" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" s="3" t="n"/>
+      <c r="K182" s="3" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Clip_Mag_X</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C183" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F183" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I183" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" s="3" t="n"/>
+      <c r="K183" s="3" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>Clip_Mag_Y</t>
+        </is>
+      </c>
+      <c r="B184" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I184" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J184" s="3" t="n"/>
+      <c r="K184" s="3" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Clip_Mag_Z</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I185" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" s="3" t="n"/>
+      <c r="K185" s="3" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="inlineStr">
+        <is>
+          <t>Clipping_Indication</t>
+        </is>
+      </c>
+      <c r="B186" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C186" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F186" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I186" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J186" s="3" t="n"/>
+      <c r="K186" s="3" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="3" t="inlineStr">
+        <is>
+          <t>SyncIn_Marker</t>
+        </is>
+      </c>
+      <c r="B187" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="C187" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F187" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I187" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" s="3" t="n"/>
+      <c r="K187" s="3" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="3" t="inlineStr">
+        <is>
+          <t>SyncOut_Marker</t>
+        </is>
+      </c>
+      <c r="B188" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="C188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J188" s="3" t="n"/>
+      <c r="K188" s="3" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="inlineStr">
+        <is>
+          <t>Filter_Mode</t>
+        </is>
+      </c>
+      <c r="B189" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="C189" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F189" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I189" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="J189" s="3" t="n"/>
+      <c r="K189" s="3" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>GNSS_Time_Pulse</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="C190" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F190" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I190" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J190" s="3" t="n"/>
+      <c r="K190" s="3" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
+        <is>
+          <t>RTK_Status</t>
+        </is>
+      </c>
+      <c r="B191" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="C191" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F191" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J191" s="3" t="n"/>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>0=No_RTK, 1=RTK_Floating, 2=RTK_Fixed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dbc_signals.xlsx
+++ b/dbc_signals.xlsx
@@ -34884,7 +34884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K191"/>
+  <dimension ref="A1:K207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -40922,6 +40922,504 @@
           <t>0=No_RTK, 1=RTK_Floating, 2=RTK_Fixed</t>
         </is>
       </c>
+    </row>
+    <row r="192"/>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_Temperature</t>
+        </is>
+      </c>
+      <c r="B193" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x538</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H194" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
+      <c r="B195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G195" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I195" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J195" s="3" t="inlineStr">
+        <is>
+          <t>degC</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr"/>
+    </row>
+    <row r="196"/>
+    <row r="197">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_Filter_Velocity</t>
+        </is>
+      </c>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x539</t>
+        </is>
+      </c>
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H198" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J198" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K198" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>Velocity_X</t>
+        </is>
+      </c>
+      <c r="B199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C199" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E199" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G199" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I199" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J199" s="3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>Velocity_Y</t>
+        </is>
+      </c>
+      <c r="B200" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C200" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E200" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G200" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I200" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J200" s="3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>Velocity_Z</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C201" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E201" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G201" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I201" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J201" s="3" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr"/>
+    </row>
+    <row r="202"/>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
+          <t>Message: IMU_Free_Acceleration</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
+          <t>ID: 0x53a</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t>Sender(s): JETSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Signal Name</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Start Bit</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Length (bits)</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Byte Order</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Signed</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Offset</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="K204" s="2" t="inlineStr">
+        <is>
+          <t>Choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>Free_Acceleration_X</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C205" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E205" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G205" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I205" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J205" s="3" t="inlineStr">
+        <is>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>Free_Acceleration_Y</t>
+        </is>
+      </c>
+      <c r="B206" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="C206" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E206" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G206" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I206" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J206" s="3" t="inlineStr">
+        <is>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>Free_Acceleration_Z</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="C207" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="E207" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G207" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" s="3" t="n">
+        <v>-327.68</v>
+      </c>
+      <c r="I207" s="3" t="n">
+        <v>327.67</v>
+      </c>
+      <c r="J207" s="3" t="inlineStr">
+        <is>
+          <t>m/s^2</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
